--- a/data/semanas/319.xlsx
+++ b/data/semanas/319.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL24"/>
+  <dimension ref="A1:AL43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3794,6 +3794,2626 @@
         <v>1</v>
       </c>
       <c r="AL24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>16849340</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Rua MONTEVIDEO</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>340 - R</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>11/08/2026 13:52</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>11/08/2026 13:56</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>46245.57777777778</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>46245.58055555556</v>
+      </c>
+      <c r="P25" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R25" t="n">
+        <v>319</v>
+      </c>
+      <c r="S25" t="n">
+        <v>32</v>
+      </c>
+      <c r="T25" t="b">
+        <v>0</v>
+      </c>
+      <c r="U25" t="b">
+        <v>0</v>
+      </c>
+      <c r="V25" t="b">
+        <v>0</v>
+      </c>
+      <c r="W25" t="b">
+        <v>0</v>
+      </c>
+      <c r="X25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>832</v>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>16849341</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Rua MONTEVIDEO</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>340 - 1 - R</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>11/08/2026 13:56</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>11/08/2026 14:01</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>46245.58055555556</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>46245.58402777778</v>
+      </c>
+      <c r="P26" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R26" t="n">
+        <v>319</v>
+      </c>
+      <c r="S26" t="n">
+        <v>32</v>
+      </c>
+      <c r="T26" t="b">
+        <v>0</v>
+      </c>
+      <c r="U26" t="b">
+        <v>0</v>
+      </c>
+      <c r="V26" t="b">
+        <v>0</v>
+      </c>
+      <c r="W26" t="b">
+        <v>0</v>
+      </c>
+      <c r="X26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>836</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>16849342</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Rua MONTEVIDEO</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>340 - 2 - R</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>11/08/2026 14:02</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>11/08/2026 14:05</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>46245.58472222222</v>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>46245.58680555555</v>
+      </c>
+      <c r="P27" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R27" t="n">
+        <v>319</v>
+      </c>
+      <c r="S27" t="n">
+        <v>32</v>
+      </c>
+      <c r="T27" t="b">
+        <v>0</v>
+      </c>
+      <c r="U27" t="b">
+        <v>0</v>
+      </c>
+      <c r="V27" t="b">
+        <v>0</v>
+      </c>
+      <c r="W27" t="b">
+        <v>0</v>
+      </c>
+      <c r="X27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>360</v>
+      </c>
+      <c r="AB27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>842</v>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>16849343</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Rua MONTEVIDEO</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>370 - R</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>11/08/2026 14:06</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>11/08/2026 14:10</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>46245.5875</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>46245.59027777778</v>
+      </c>
+      <c r="P28" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q28" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R28" t="n">
+        <v>319</v>
+      </c>
+      <c r="S28" t="n">
+        <v>32</v>
+      </c>
+      <c r="T28" t="b">
+        <v>0</v>
+      </c>
+      <c r="U28" t="b">
+        <v>0</v>
+      </c>
+      <c r="V28" t="b">
+        <v>0</v>
+      </c>
+      <c r="W28" t="b">
+        <v>0</v>
+      </c>
+      <c r="X28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>846</v>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>16849344</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Rua MONTEVIDEO</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>400 - R</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>11/08/2026 14:14</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>11/08/2026 14:21</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>46245.59305555555</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>46245.59791666667</v>
+      </c>
+      <c r="P29" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q29" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R29" t="n">
+        <v>319</v>
+      </c>
+      <c r="S29" t="n">
+        <v>32</v>
+      </c>
+      <c r="T29" t="b">
+        <v>0</v>
+      </c>
+      <c r="U29" t="b">
+        <v>0</v>
+      </c>
+      <c r="V29" t="b">
+        <v>0</v>
+      </c>
+      <c r="W29" t="b">
+        <v>0</v>
+      </c>
+      <c r="X29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>480</v>
+      </c>
+      <c r="AB29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>854</v>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>16849345</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Rua MONTEVIDEO</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>410 - OU</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>11/08/2026 14:21</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>11/08/2026 14:29</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>46245.59791666667</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>46245.60347222222</v>
+      </c>
+      <c r="P30" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q30" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R30" t="n">
+        <v>319</v>
+      </c>
+      <c r="S30" t="n">
+        <v>32</v>
+      </c>
+      <c r="T30" t="b">
+        <v>0</v>
+      </c>
+      <c r="U30" t="b">
+        <v>0</v>
+      </c>
+      <c r="V30" t="b">
+        <v>0</v>
+      </c>
+      <c r="W30" t="b">
+        <v>0</v>
+      </c>
+      <c r="X30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>420</v>
+      </c>
+      <c r="AB30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>861</v>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>16849346</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Rua MONTEVIDEO</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>380 - OU</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>11/08/2026 14:29</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>11/08/2026 14:32</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>46245.60347222222</v>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>46245.60555555556</v>
+      </c>
+      <c r="P31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R31" t="n">
+        <v>319</v>
+      </c>
+      <c r="S31" t="n">
+        <v>32</v>
+      </c>
+      <c r="T31" t="b">
+        <v>0</v>
+      </c>
+      <c r="U31" t="b">
+        <v>0</v>
+      </c>
+      <c r="V31" t="b">
+        <v>0</v>
+      </c>
+      <c r="W31" t="b">
+        <v>0</v>
+      </c>
+      <c r="X31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>480</v>
+      </c>
+      <c r="AB31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>869</v>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>16849347</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Q030</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Rua MONTEVIDEO</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>01 - TB</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>11/08/2026 14:33</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>11/08/2026 14:40</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>46245.60625</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>46245.61111111111</v>
+      </c>
+      <c r="P32" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q32" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R32" t="n">
+        <v>319</v>
+      </c>
+      <c r="S32" t="n">
+        <v>32</v>
+      </c>
+      <c r="T32" t="b">
+        <v>0</v>
+      </c>
+      <c r="U32" t="b">
+        <v>0</v>
+      </c>
+      <c r="V32" t="b">
+        <v>0</v>
+      </c>
+      <c r="W32" t="b">
+        <v>0</v>
+      </c>
+      <c r="X32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>873</v>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>16849348</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Rua ROBERTO BUENO DA SILVA</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>621 - 1 - R</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>11/08/2026 14:41</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>11/08/2026 14:47</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>46245.61180555556</v>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>46245.61597222222</v>
+      </c>
+      <c r="P33" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q33" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R33" t="n">
+        <v>319</v>
+      </c>
+      <c r="S33" t="n">
+        <v>32</v>
+      </c>
+      <c r="T33" t="b">
+        <v>0</v>
+      </c>
+      <c r="U33" t="b">
+        <v>0</v>
+      </c>
+      <c r="V33" t="b">
+        <v>0</v>
+      </c>
+      <c r="W33" t="b">
+        <v>0</v>
+      </c>
+      <c r="X33" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>480</v>
+      </c>
+      <c r="AB33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>881</v>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>16849349</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Rua ROBERTO BUENO DA SILVA</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>621 - 2 - TB</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>11/08/2026 14:47</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>11/08/2026 14:58</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>46245.61597222222</v>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>46245.62361111111</v>
+      </c>
+      <c r="P34" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q34" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R34" t="n">
+        <v>319</v>
+      </c>
+      <c r="S34" t="n">
+        <v>32</v>
+      </c>
+      <c r="T34" t="b">
+        <v>0</v>
+      </c>
+      <c r="U34" t="b">
+        <v>0</v>
+      </c>
+      <c r="V34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W34" t="b">
+        <v>0</v>
+      </c>
+      <c r="X34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>360</v>
+      </c>
+      <c r="AB34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>887</v>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>16849350</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Rua ROBERTO BUENO DA SILVA</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>609 - R</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>11/08/2026 14:59</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>11/08/2026 15:05</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>46245.62430555555</v>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>46245.62847222222</v>
+      </c>
+      <c r="P35" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R35" t="n">
+        <v>319</v>
+      </c>
+      <c r="S35" t="n">
+        <v>32</v>
+      </c>
+      <c r="T35" t="b">
+        <v>0</v>
+      </c>
+      <c r="U35" t="b">
+        <v>0</v>
+      </c>
+      <c r="V35" t="b">
+        <v>0</v>
+      </c>
+      <c r="W35" t="b">
+        <v>0</v>
+      </c>
+      <c r="X35" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>720</v>
+      </c>
+      <c r="AB35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>899</v>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>16849351</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Rua ROBERTO BUENO DA SILVA</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>597 - R</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>11/08/2026 15:06</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>11/08/2026 15:14</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>46245.62916666667</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>46245.63472222222</v>
+      </c>
+      <c r="P36" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R36" t="n">
+        <v>319</v>
+      </c>
+      <c r="S36" t="n">
+        <v>32</v>
+      </c>
+      <c r="T36" t="b">
+        <v>0</v>
+      </c>
+      <c r="U36" t="b">
+        <v>0</v>
+      </c>
+      <c r="V36" t="b">
+        <v>0</v>
+      </c>
+      <c r="W36" t="b">
+        <v>0</v>
+      </c>
+      <c r="X36" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>420</v>
+      </c>
+      <c r="AB36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>906</v>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>16849352</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Rua ROBERTO BUENO DA SILVA</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>587 - R</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>11/08/2026 15:16</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>11/08/2026 15:24</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>46245.63611111111</v>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>46245.64166666667</v>
+      </c>
+      <c r="P37" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q37" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R37" t="n">
+        <v>319</v>
+      </c>
+      <c r="S37" t="n">
+        <v>32</v>
+      </c>
+      <c r="T37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U37" t="b">
+        <v>0</v>
+      </c>
+      <c r="V37" t="b">
+        <v>0</v>
+      </c>
+      <c r="W37" t="b">
+        <v>0</v>
+      </c>
+      <c r="X37" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>600</v>
+      </c>
+      <c r="AB37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>916</v>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>16849353</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Avenida COSTA E SILVA</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>573 - 1 - R</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>11/08/2026 15:35</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>11/08/2026 15:39</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>46245.64930555555</v>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v>46245.65208333333</v>
+      </c>
+      <c r="P38" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q38" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R38" t="n">
+        <v>319</v>
+      </c>
+      <c r="S38" t="n">
+        <v>32</v>
+      </c>
+      <c r="T38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U38" t="b">
+        <v>0</v>
+      </c>
+      <c r="V38" t="b">
+        <v>0</v>
+      </c>
+      <c r="W38" t="b">
+        <v>0</v>
+      </c>
+      <c r="X38" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1140</v>
+      </c>
+      <c r="AB38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>935</v>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>16849354</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Avenida COSTA E SILVA</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>570 - R</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>11/08/2026 15:41</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>11/08/2026 15:45</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>46245.65347222222</v>
+      </c>
+      <c r="O39" s="2" t="n">
+        <v>46245.65625</v>
+      </c>
+      <c r="P39" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q39" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R39" t="n">
+        <v>319</v>
+      </c>
+      <c r="S39" t="n">
+        <v>32</v>
+      </c>
+      <c r="T39" t="b">
+        <v>0</v>
+      </c>
+      <c r="U39" t="b">
+        <v>0</v>
+      </c>
+      <c r="V39" t="b">
+        <v>0</v>
+      </c>
+      <c r="W39" t="b">
+        <v>0</v>
+      </c>
+      <c r="X39" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>360</v>
+      </c>
+      <c r="AB39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>941</v>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>16849355</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Avenida COSTA E SILVA</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>582 - R</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>11/08/2026 15:45</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>11/08/2026 15:48</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>46245.65625</v>
+      </c>
+      <c r="O40" s="2" t="n">
+        <v>46245.65833333333</v>
+      </c>
+      <c r="P40" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q40" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R40" t="n">
+        <v>319</v>
+      </c>
+      <c r="S40" t="n">
+        <v>32</v>
+      </c>
+      <c r="T40" t="b">
+        <v>0</v>
+      </c>
+      <c r="U40" t="b">
+        <v>0</v>
+      </c>
+      <c r="V40" t="b">
+        <v>0</v>
+      </c>
+      <c r="W40" t="b">
+        <v>0</v>
+      </c>
+      <c r="X40" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>945</v>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>16849356</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Avenida COSTA E SILVA</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>606 - C</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>11/08/2026 15:48</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>11/08/2026 15:51</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>46245.65833333333</v>
+      </c>
+      <c r="O41" s="2" t="n">
+        <v>46245.66041666667</v>
+      </c>
+      <c r="P41" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R41" t="n">
+        <v>319</v>
+      </c>
+      <c r="S41" t="n">
+        <v>32</v>
+      </c>
+      <c r="T41" t="b">
+        <v>0</v>
+      </c>
+      <c r="U41" t="b">
+        <v>0</v>
+      </c>
+      <c r="V41" t="b">
+        <v>0</v>
+      </c>
+      <c r="W41" t="b">
+        <v>0</v>
+      </c>
+      <c r="X41" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>948</v>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>16849357</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Rua ROBERTO BUENO DA SILVA</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>573 - R</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>11/08/2026 15:56</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>11/08/2026 16:00</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>46245.66388888889</v>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v>46245.66666666666</v>
+      </c>
+      <c r="P42" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q42" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R42" t="n">
+        <v>319</v>
+      </c>
+      <c r="S42" t="n">
+        <v>32</v>
+      </c>
+      <c r="T42" t="b">
+        <v>0</v>
+      </c>
+      <c r="U42" t="b">
+        <v>0</v>
+      </c>
+      <c r="V42" t="b">
+        <v>0</v>
+      </c>
+      <c r="W42" t="b">
+        <v>0</v>
+      </c>
+      <c r="X42" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>480</v>
+      </c>
+      <c r="AB42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>956</v>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>16849358</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Rua ROBERTO BUENO DA SILVA</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>621 - C</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>11/08/2026 16:00</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>11/08/2026 16:05</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>46245.66666666666</v>
+      </c>
+      <c r="O43" s="2" t="n">
+        <v>46245.67013888889</v>
+      </c>
+      <c r="P43" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q43" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R43" t="n">
+        <v>319</v>
+      </c>
+      <c r="S43" t="n">
+        <v>32</v>
+      </c>
+      <c r="T43" t="b">
+        <v>0</v>
+      </c>
+      <c r="U43" t="b">
+        <v>0</v>
+      </c>
+      <c r="V43" t="b">
+        <v>0</v>
+      </c>
+      <c r="W43" t="b">
+        <v>0</v>
+      </c>
+      <c r="X43" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>960</v>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK43" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL43" t="b">
         <v>0</v>
       </c>
     </row>

--- a/data/semanas/319.xlsx
+++ b/data/semanas/319.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL43"/>
+  <dimension ref="A1:AL58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1179,7 +1179,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>16847462</v>
+        <v>16850102</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>408 - PARQUE DE EXPOSIÇÕES</t>
+          <t>409 - ANDREAZZA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Q034</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>735 - R</t>
+          <t>806 - R</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1213,25 +1213,25 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Recuperação</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>11/08/2026 09:56</t>
+          <t>11/08/2026 10:19</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11/08/2026 10:01</t>
+          <t>11/08/2026 10:21</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>30</v>
+        <v>3101</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Carlos Alberto Albiero</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="N6" s="2" t="n">
-        <v>46245.41388888889</v>
+        <v>46245.42986111111</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>46245.41736111111</v>
+        <v>46245.43125</v>
       </c>
       <c r="P6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>46245</v>
@@ -1258,7 +1258,7 @@
         <v>32</v>
       </c>
       <c r="T6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
@@ -1287,10 +1287,10 @@
       </c>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF6" t="n">
-        <v>596</v>
+        <v>619</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>16847463</v>
+        <v>16847462</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Q035</t>
+          <t>Q034</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>718 - R</t>
+          <t>735 - R</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1349,17 +1349,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Recuperação</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11/08/2026 10:02</t>
+          <t>11/08/2026 09:56</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11/08/2026 10:06</t>
+          <t>11/08/2026 10:01</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -1376,13 +1376,13 @@
         </is>
       </c>
       <c r="N7" s="2" t="n">
-        <v>46245.41805555556</v>
+        <v>46245.41388888889</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>46245.42083333333</v>
+        <v>46245.41736111111</v>
       </c>
       <c r="P7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>46245</v>
@@ -1414,9 +1414,7 @@
       <c r="Z7" t="b">
         <v>0</v>
       </c>
-      <c r="AA7" t="n">
-        <v>360</v>
-      </c>
+      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="b">
         <v>0</v>
       </c>
@@ -1425,10 +1423,10 @@
       </c>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF7" t="n">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
@@ -1453,7 +1451,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>16847464</v>
+        <v>16847463</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1467,7 +1465,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Q034</t>
+          <t>Q035</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1477,7 +1475,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>713 - R</t>
+          <t>718 - R</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1487,17 +1485,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Recuperação</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>11/08/2026 10:07</t>
+          <t>11/08/2026 10:02</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>11/08/2026 10:12</t>
+          <t>11/08/2026 10:06</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -1514,13 +1512,13 @@
         </is>
       </c>
       <c r="N8" s="2" t="n">
-        <v>46245.42152777778</v>
+        <v>46245.41805555556</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>46245.425</v>
+        <v>46245.42083333333</v>
       </c>
       <c r="P8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>46245</v>
@@ -1553,7 +1551,7 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="AB8" t="b">
         <v>0</v>
@@ -1566,7 +1564,7 @@
         <v>10</v>
       </c>
       <c r="AF8" t="n">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
@@ -1591,7 +1589,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>16847465</v>
+        <v>16847464</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1615,7 +1613,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>713 - 2 - R</t>
+          <t>713 - R</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1630,12 +1628,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>11/08/2026 10:07</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>11/08/2026 10:12</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>11/08/2026 10:15</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1652,13 +1650,13 @@
         </is>
       </c>
       <c r="N9" s="2" t="n">
+        <v>46245.42152777778</v>
+      </c>
+      <c r="O9" s="2" t="n">
         <v>46245.425</v>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>46245.42708333334</v>
-      </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>46245</v>
@@ -1704,7 +1702,7 @@
         <v>10</v>
       </c>
       <c r="AF9" t="n">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
@@ -1729,7 +1727,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>16847466</v>
+        <v>16847465</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1753,7 +1751,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>713 - 1 - R</t>
+          <t>713 - 2 - R</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1768,12 +1766,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>11/08/2026 10:16</t>
+          <t>11/08/2026 10:12</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>11/08/2026 10:23</t>
+          <t>11/08/2026 10:15</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1790,13 +1788,13 @@
         </is>
       </c>
       <c r="N10" s="2" t="n">
-        <v>46245.42777777778</v>
+        <v>46245.425</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>46245.43263888889</v>
+        <v>46245.42708333334</v>
       </c>
       <c r="P10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>46245</v>
@@ -1829,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="AB10" t="b">
         <v>0</v>
@@ -1842,7 +1840,7 @@
         <v>10</v>
       </c>
       <c r="AF10" t="n">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
@@ -1867,7 +1865,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>16847467</v>
+        <v>16847466</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1891,7 +1889,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>701 - C</t>
+          <t>713 - 1 - R</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1906,12 +1904,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>11/08/2026 10:16</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>11/08/2026 10:23</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>11/08/2026 10:26</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1928,13 +1926,13 @@
         </is>
       </c>
       <c r="N11" s="2" t="n">
+        <v>46245.42777777778</v>
+      </c>
+      <c r="O11" s="2" t="n">
         <v>46245.43263888889</v>
       </c>
-      <c r="O11" s="2" t="n">
-        <v>46245.43472222222</v>
-      </c>
       <c r="P11" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>46245</v>
@@ -1967,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>420</v>
+        <v>240</v>
       </c>
       <c r="AB11" t="b">
         <v>0</v>
@@ -1980,7 +1978,7 @@
         <v>10</v>
       </c>
       <c r="AF11" t="n">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
@@ -2005,7 +2003,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>16847468</v>
+        <v>16847467</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2029,7 +2027,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>701 - 1 - R</t>
+          <t>701 - C</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2044,12 +2042,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>11/08/2026 10:27</t>
+          <t>11/08/2026 10:23</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>11/08/2026 10:30</t>
+          <t>11/08/2026 10:26</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -2066,10 +2064,10 @@
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>46245.43541666667</v>
+        <v>46245.43263888889</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>46245.4375</v>
+        <v>46245.43472222222</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -2105,7 +2103,7 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>240</v>
+        <v>420</v>
       </c>
       <c r="AB12" t="b">
         <v>0</v>
@@ -2118,7 +2116,7 @@
         <v>10</v>
       </c>
       <c r="AF12" t="n">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
@@ -2143,7 +2141,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>16847471</v>
+        <v>16847468</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -2167,7 +2165,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>689 - R</t>
+          <t>701 - 1 - R</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2182,12 +2180,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>11/08/2026 10:27</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>11/08/2026 10:30</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>11/08/2026 10:38</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -2204,13 +2202,13 @@
         </is>
       </c>
       <c r="N13" s="2" t="n">
+        <v>46245.43541666667</v>
+      </c>
+      <c r="O13" s="2" t="n">
         <v>46245.4375</v>
       </c>
-      <c r="O13" s="2" t="n">
-        <v>46245.44305555556</v>
-      </c>
       <c r="P13" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>46245</v>
@@ -2243,7 +2241,7 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="AB13" t="b">
         <v>0</v>
@@ -2256,7 +2254,7 @@
         <v>10</v>
       </c>
       <c r="AF13" t="n">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
@@ -2281,7 +2279,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>16847472</v>
+        <v>16847471</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2305,7 +2303,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>653 - C</t>
+          <t>689 - R</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2320,12 +2318,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t>11/08/2026 10:30</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>11/08/2026 10:38</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>11/08/2026 10:44</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -2342,13 +2340,13 @@
         </is>
       </c>
       <c r="N14" s="2" t="n">
+        <v>46245.4375</v>
+      </c>
+      <c r="O14" s="2" t="n">
         <v>46245.44305555556</v>
       </c>
-      <c r="O14" s="2" t="n">
-        <v>46245.44722222222</v>
-      </c>
       <c r="P14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>46245</v>
@@ -2381,7 +2379,7 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>480</v>
+        <v>180</v>
       </c>
       <c r="AB14" t="b">
         <v>0</v>
@@ -2394,7 +2392,7 @@
         <v>10</v>
       </c>
       <c r="AF14" t="n">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
@@ -2419,7 +2417,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>16847473</v>
+        <v>16847472</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2443,7 +2441,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>653 - 1 - C</t>
+          <t>653 - C</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2458,12 +2456,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t>11/08/2026 10:38</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>11/08/2026 10:44</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>11/08/2026 10:47</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -2480,13 +2478,13 @@
         </is>
       </c>
       <c r="N15" s="2" t="n">
+        <v>46245.44305555556</v>
+      </c>
+      <c r="O15" s="2" t="n">
         <v>46245.44722222222</v>
       </c>
-      <c r="O15" s="2" t="n">
-        <v>46245.44930555556</v>
-      </c>
       <c r="P15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>46245</v>
@@ -2519,7 +2517,7 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>360</v>
+        <v>480</v>
       </c>
       <c r="AB15" t="b">
         <v>0</v>
@@ -2532,7 +2530,7 @@
         <v>10</v>
       </c>
       <c r="AF15" t="n">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
@@ -2557,7 +2555,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>16847474</v>
+        <v>16847473</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2581,7 +2579,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>653 - 2 - C</t>
+          <t>653 - 1 - C</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2596,12 +2594,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>11/08/2026 10:48</t>
+          <t>11/08/2026 10:44</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>11/08/2026 10:51</t>
+          <t>11/08/2026 10:47</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -2618,10 +2616,10 @@
         </is>
       </c>
       <c r="N16" s="2" t="n">
-        <v>46245.45</v>
+        <v>46245.44722222222</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>46245.45208333333</v>
+        <v>46245.44930555556</v>
       </c>
       <c r="P16" t="n">
         <v>3</v>
@@ -2657,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
       <c r="AB16" t="b">
         <v>0</v>
@@ -2670,7 +2668,7 @@
         <v>10</v>
       </c>
       <c r="AF16" t="n">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
@@ -2695,7 +2693,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16847475</v>
+        <v>16847474</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2719,7 +2717,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>653 - 3 - C</t>
+          <t>653 - 2 - C</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2734,12 +2732,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t>11/08/2026 10:48</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>11/08/2026 10:51</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>11/08/2026 10:55</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -2756,13 +2754,13 @@
         </is>
       </c>
       <c r="N17" s="2" t="n">
+        <v>46245.45</v>
+      </c>
+      <c r="O17" s="2" t="n">
         <v>46245.45208333333</v>
       </c>
-      <c r="O17" s="2" t="n">
-        <v>46245.45486111111</v>
-      </c>
       <c r="P17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>46245</v>
@@ -2795,7 +2793,7 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="AB17" t="b">
         <v>0</v>
@@ -2808,7 +2806,7 @@
         <v>10</v>
       </c>
       <c r="AF17" t="n">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
@@ -2833,7 +2831,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>16847476</v>
+        <v>16847475</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2857,7 +2855,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>653 - 4 - C</t>
+          <t>653 - 3 - C</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2872,12 +2870,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
+          <t>11/08/2026 10:51</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>11/08/2026 10:55</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>11/08/2026 10:59</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -2894,10 +2892,10 @@
         </is>
       </c>
       <c r="N18" s="2" t="n">
+        <v>46245.45208333333</v>
+      </c>
+      <c r="O18" s="2" t="n">
         <v>46245.45486111111</v>
-      </c>
-      <c r="O18" s="2" t="n">
-        <v>46245.45763888889</v>
       </c>
       <c r="P18" t="n">
         <v>4</v>
@@ -2933,7 +2931,7 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="AB18" t="b">
         <v>0</v>
@@ -2946,7 +2944,7 @@
         <v>10</v>
       </c>
       <c r="AF18" t="n">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
@@ -2971,7 +2969,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>16847477</v>
+        <v>16847476</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2985,17 +2983,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Q019</t>
+          <t>Q034</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rua CORONEL PONCE</t>
+          <t>Rua DIGNO TORRES GIMENEZ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>562 - R</t>
+          <t>653 - 4 - C</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -3005,17 +3003,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Recuperação</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>11/08/2026 12:55</t>
+          <t>11/08/2026 10:55</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>11/08/2026 12:58</t>
+          <t>11/08/2026 10:59</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -3032,13 +3030,13 @@
         </is>
       </c>
       <c r="N19" s="2" t="n">
-        <v>46245.53819444445</v>
+        <v>46245.45486111111</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>46245.54027777778</v>
+        <v>46245.45763888889</v>
       </c>
       <c r="P19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>46245</v>
@@ -3071,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>7200</v>
+        <v>240</v>
       </c>
       <c r="AB19" t="b">
         <v>0</v>
@@ -3081,14 +3079,14 @@
       </c>
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AF19" t="n">
-        <v>775</v>
+        <v>655</v>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="AH19" t="b">
@@ -3101,15 +3099,15 @@
         <v>0</v>
       </c>
       <c r="AK19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>16847480</v>
+        <v>16847477</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -3123,17 +3121,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Q034</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rua RAUL PEREIRA</t>
+          <t>Rua CORONEL PONCE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>653 - 7 - OU</t>
+          <t>562 - R</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3143,17 +3141,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Recuperação</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>11/08/2026 13:09</t>
+          <t>11/08/2026 12:55</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>11/08/2026 13:13</t>
+          <t>11/08/2026 12:58</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -3170,13 +3168,13 @@
         </is>
       </c>
       <c r="N20" s="2" t="n">
-        <v>46245.54791666667</v>
+        <v>46245.53819444445</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>46245.55069444444</v>
+        <v>46245.54027777778</v>
       </c>
       <c r="P20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>46245</v>
@@ -3209,7 +3207,7 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>840</v>
+        <v>7200</v>
       </c>
       <c r="AB20" t="b">
         <v>0</v>
@@ -3219,10 +3217,10 @@
       </c>
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF20" t="n">
-        <v>789</v>
+        <v>775</v>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
@@ -3239,15 +3237,15 @@
         <v>0</v>
       </c>
       <c r="AK20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>16847481</v>
+        <v>16847480</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -3271,7 +3269,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>653 - 8 - OU</t>
+          <t>653 - 7 - OU</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3286,12 +3284,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
+          <t>11/08/2026 13:09</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
           <t>11/08/2026 13:13</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>11/08/2026 13:18</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -3308,13 +3306,13 @@
         </is>
       </c>
       <c r="N21" s="2" t="n">
+        <v>46245.54791666667</v>
+      </c>
+      <c r="O21" s="2" t="n">
         <v>46245.55069444444</v>
       </c>
-      <c r="O21" s="2" t="n">
-        <v>46245.55416666667</v>
-      </c>
       <c r="P21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>46245</v>
@@ -3347,7 +3345,7 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>240</v>
+        <v>840</v>
       </c>
       <c r="AB21" t="b">
         <v>0</v>
@@ -3360,7 +3358,7 @@
         <v>13</v>
       </c>
       <c r="AF21" t="n">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
@@ -3385,7 +3383,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>16847482</v>
+        <v>16847481</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -3409,7 +3407,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>653 - 9 - OU</t>
+          <t>653 - 8 - OU</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3424,12 +3422,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
+          <t>11/08/2026 13:13</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
           <t>11/08/2026 13:18</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>11/08/2026 13:22</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -3446,13 +3444,13 @@
         </is>
       </c>
       <c r="N22" s="2" t="n">
+        <v>46245.55069444444</v>
+      </c>
+      <c r="O22" s="2" t="n">
         <v>46245.55416666667</v>
       </c>
-      <c r="O22" s="2" t="n">
-        <v>46245.55694444444</v>
-      </c>
       <c r="P22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>46245</v>
@@ -3485,7 +3483,7 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="AB22" t="b">
         <v>0</v>
@@ -3498,7 +3496,7 @@
         <v>13</v>
       </c>
       <c r="AF22" t="n">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
@@ -3523,7 +3521,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>16847483</v>
+        <v>16847482</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3547,7 +3545,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>653 - 10 - OU</t>
+          <t>653 - 9 - OU</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3562,12 +3560,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
+          <t>11/08/2026 13:18</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
           <t>11/08/2026 13:22</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>11/08/2026 13:27</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -3584,13 +3582,13 @@
         </is>
       </c>
       <c r="N23" s="2" t="n">
+        <v>46245.55416666667</v>
+      </c>
+      <c r="O23" s="2" t="n">
         <v>46245.55694444444</v>
       </c>
-      <c r="O23" s="2" t="n">
-        <v>46245.56041666667</v>
-      </c>
       <c r="P23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q23" s="3" t="n">
         <v>46245</v>
@@ -3623,7 +3621,7 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="AB23" t="b">
         <v>0</v>
@@ -3636,7 +3634,7 @@
         <v>13</v>
       </c>
       <c r="AF23" t="n">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
@@ -3661,7 +3659,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>16847484</v>
+        <v>16847483</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3685,7 +3683,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>653 - 11 - OU</t>
+          <t>653 - 10 - OU</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3700,12 +3698,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
+          <t>11/08/2026 13:22</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t>11/08/2026 13:27</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>11/08/2026 13:29</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -3722,13 +3720,13 @@
         </is>
       </c>
       <c r="N24" s="2" t="n">
+        <v>46245.55694444444</v>
+      </c>
+      <c r="O24" s="2" t="n">
         <v>46245.56041666667</v>
       </c>
-      <c r="O24" s="2" t="n">
-        <v>46245.56180555555</v>
-      </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>46245</v>
@@ -3740,7 +3738,7 @@
         <v>32</v>
       </c>
       <c r="T24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U24" t="b">
         <v>0</v>
@@ -3761,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="AB24" t="b">
         <v>0</v>
@@ -3774,7 +3772,7 @@
         <v>13</v>
       </c>
       <c r="AF24" t="n">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
@@ -3799,7 +3797,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>16849340</v>
+        <v>16847484</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3808,22 +3806,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>408 - PARQUE DE EXPOSIÇÕES</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Q031</t>
+          <t>Q034</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rua MONTEVIDEO</t>
+          <t>Rua RAUL PEREIRA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>340 - R</t>
+          <t>653 - 11 - OU</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3838,35 +3836,35 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>11/08/2026 13:52</t>
+          <t>11/08/2026 13:27</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>11/08/2026 13:56</t>
+          <t>11/08/2026 13:29</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>2721</v>
+        <v>30</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="N25" s="2" t="n">
-        <v>46245.57777777778</v>
+        <v>46245.56041666667</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>46245.58055555556</v>
+        <v>46245.56180555555</v>
       </c>
       <c r="P25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q25" s="3" t="n">
         <v>46245</v>
@@ -3878,7 +3876,7 @@
         <v>32</v>
       </c>
       <c r="T25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" t="b">
         <v>0</v>
@@ -3898,7 +3896,9 @@
       <c r="Z25" t="b">
         <v>0</v>
       </c>
-      <c r="AA25" t="inlineStr"/>
+      <c r="AA25" t="n">
+        <v>300</v>
+      </c>
       <c r="AB25" t="b">
         <v>0</v>
       </c>
@@ -3910,7 +3910,7 @@
         <v>13</v>
       </c>
       <c r="AF25" t="n">
-        <v>832</v>
+        <v>807</v>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>16849341</v>
+        <v>16852016</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3944,22 +3944,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>415 - CENTRO 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Q031</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rua MONTEVIDEO</t>
+          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>340 - 1 - R</t>
+          <t>1484 - 4 - R - 104</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3974,35 +3974,35 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>11/08/2026 13:56</t>
+          <t>11/08/2026 08:05</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>11/08/2026 14:01</t>
+          <t>11/08/2026 08:08</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>2721</v>
+        <v>2030</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="N26" s="2" t="n">
-        <v>46245.58055555556</v>
+        <v>46245.33680555555</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>46245.58402777778</v>
+        <v>46245.33888888889</v>
       </c>
       <c r="P26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>46245</v>
@@ -4034,9 +4034,7 @@
       <c r="Z26" t="b">
         <v>0</v>
       </c>
-      <c r="AA26" t="n">
-        <v>240</v>
-      </c>
+      <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="b">
         <v>0</v>
       </c>
@@ -4045,14 +4043,14 @@
       </c>
       <c r="AD26" t="inlineStr"/>
       <c r="AE26" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AF26" t="n">
-        <v>836</v>
+        <v>485</v>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="AH26" t="b">
@@ -4073,7 +4071,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>16849342</v>
+        <v>16852018</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -4082,22 +4080,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>415 - CENTRO 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Q031</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rua MONTEVIDEO</t>
+          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>340 - 2 - R</t>
+          <t>1484 - 5 - R</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4112,35 +4110,35 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>11/08/2026 14:02</t>
+          <t>11/08/2026 08:08</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>11/08/2026 14:05</t>
+          <t>11/08/2026 08:12</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>2721</v>
+        <v>2030</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="N27" s="2" t="n">
-        <v>46245.58472222222</v>
+        <v>46245.33888888889</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>46245.58680555555</v>
+        <v>46245.34166666667</v>
       </c>
       <c r="P27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>46245</v>
@@ -4173,7 +4171,7 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>360</v>
+        <v>180</v>
       </c>
       <c r="AB27" t="b">
         <v>0</v>
@@ -4183,14 +4181,14 @@
       </c>
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AF27" t="n">
-        <v>842</v>
+        <v>488</v>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="AH27" t="b">
@@ -4211,7 +4209,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>16849343</v>
+        <v>16852020</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -4220,22 +4218,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>415 - CENTRO 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Q031</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rua MONTEVIDEO</t>
+          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>370 - R</t>
+          <t>1469 - 1 - C</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4250,35 +4248,35 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>11/08/2026 14:06</t>
+          <t>11/08/2026 08:12</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>11/08/2026 14:10</t>
+          <t>11/08/2026 08:15</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>2721</v>
+        <v>2030</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="N28" s="2" t="n">
-        <v>46245.5875</v>
+        <v>46245.34166666667</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>46245.59027777778</v>
+        <v>46245.34375</v>
       </c>
       <c r="P28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>46245</v>
@@ -4321,14 +4319,14 @@
       </c>
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AF28" t="n">
-        <v>846</v>
+        <v>492</v>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="AH28" t="b">
@@ -4349,7 +4347,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>16849344</v>
+        <v>16852023</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -4358,22 +4356,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>415 - CENTRO 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Q031</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rua MONTEVIDEO</t>
+          <t>Rua PARAGUAI</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>400 - R</t>
+          <t>2568 - R</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4388,35 +4386,35 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>11/08/2026 14:14</t>
+          <t>11/08/2026 08:16</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>11/08/2026 14:21</t>
+          <t>11/08/2026 08:20</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>2721</v>
+        <v>2030</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="N29" s="2" t="n">
-        <v>46245.59305555555</v>
+        <v>46245.34444444445</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>46245.59791666667</v>
+        <v>46245.34722222222</v>
       </c>
       <c r="P29" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>46245</v>
@@ -4449,7 +4447,7 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>480</v>
+        <v>240</v>
       </c>
       <c r="AB29" t="b">
         <v>0</v>
@@ -4459,14 +4457,14 @@
       </c>
       <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AF29" t="n">
-        <v>854</v>
+        <v>496</v>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="AH29" t="b">
@@ -4487,7 +4485,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>16849345</v>
+        <v>16852027</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -4496,22 +4494,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>415 - CENTRO 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Q031</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rua MONTEVIDEO</t>
+          <t>Rua PARAGUAI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>410 - OU</t>
+          <t>2598 - OU</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4526,35 +4524,35 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>11/08/2026 14:21</t>
+          <t>11/08/2026 08:20</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>11/08/2026 14:29</t>
+          <t>11/08/2026 08:25</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>2721</v>
+        <v>2030</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="N30" s="2" t="n">
-        <v>46245.59791666667</v>
+        <v>46245.34722222222</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>46245.60347222222</v>
+        <v>46245.35069444445</v>
       </c>
       <c r="P30" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>46245</v>
@@ -4587,7 +4585,7 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>420</v>
+        <v>240</v>
       </c>
       <c r="AB30" t="b">
         <v>0</v>
@@ -4597,14 +4595,14 @@
       </c>
       <c r="AD30" t="inlineStr"/>
       <c r="AE30" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AF30" t="n">
-        <v>861</v>
+        <v>500</v>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="AH30" t="b">
@@ -4625,7 +4623,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>16849346</v>
+        <v>16852030</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -4634,22 +4632,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>415 - CENTRO 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Q031</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rua MONTEVIDEO</t>
+          <t>Rua GUIA LOPES</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>380 - OU</t>
+          <t>278 - C</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4664,32 +4662,32 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>11/08/2026 14:29</t>
+          <t>11/08/2026 08:28</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>11/08/2026 14:32</t>
+          <t>11/08/2026 08:31</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>2721</v>
+        <v>2030</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="N31" s="2" t="n">
-        <v>46245.60347222222</v>
+        <v>46245.35277777778</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>46245.60555555556</v>
+        <v>46245.35486111111</v>
       </c>
       <c r="P31" t="n">
         <v>3</v>
@@ -4735,14 +4733,14 @@
       </c>
       <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AF31" t="n">
-        <v>869</v>
+        <v>508</v>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="AH31" t="b">
@@ -4763,7 +4761,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>16849347</v>
+        <v>16852031</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4772,22 +4770,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>415 - CENTRO 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rua MONTEVIDEO</t>
+          <t>Rua GUIA LOPES</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>01 - TB</t>
+          <t>146 - C</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4802,35 +4800,35 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>11/08/2026 14:33</t>
+          <t>11/08/2026 08:31</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>11/08/2026 14:40</t>
+          <t>11/08/2026 08:33</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>2721</v>
+        <v>2030</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="N32" s="2" t="n">
-        <v>46245.60625</v>
+        <v>46245.35486111111</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>46245.61111111111</v>
+        <v>46245.35625</v>
       </c>
       <c r="P32" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>46245</v>
@@ -4842,7 +4840,7 @@
         <v>32</v>
       </c>
       <c r="T32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U32" t="b">
         <v>0</v>
@@ -4863,7 +4861,7 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="AB32" t="b">
         <v>0</v>
@@ -4873,14 +4871,14 @@
       </c>
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AF32" t="n">
-        <v>873</v>
+        <v>511</v>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="AH32" t="b">
@@ -4901,7 +4899,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>16849348</v>
+        <v>16852032</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4910,22 +4908,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>415 - CENTRO 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Q032</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rua ROBERTO BUENO DA SILVA</t>
+          <t>Avenida BRASIL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>621 - 1 - R</t>
+          <t>2485 - R</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4940,35 +4938,35 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>11/08/2026 14:41</t>
+          <t>11/08/2026 08:35</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>11/08/2026 14:47</t>
+          <t>11/08/2026 08:40</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>2721</v>
+        <v>2030</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="N33" s="2" t="n">
-        <v>46245.61180555556</v>
+        <v>46245.35763888889</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>46245.61597222222</v>
+        <v>46245.36111111111</v>
       </c>
       <c r="P33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q33" s="3" t="n">
         <v>46245</v>
@@ -5001,7 +4999,7 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>480</v>
+        <v>240</v>
       </c>
       <c r="AB33" t="b">
         <v>0</v>
@@ -5011,14 +5009,14 @@
       </c>
       <c r="AD33" t="inlineStr"/>
       <c r="AE33" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AF33" t="n">
-        <v>881</v>
+        <v>515</v>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="AH33" t="b">
@@ -5039,7 +5037,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>16849349</v>
+        <v>16852033</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -5048,22 +5046,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>415 - CENTRO 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Q032</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rua ROBERTO BUENO DA SILVA</t>
+          <t>Avenida BRASIL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>621 - 2 - TB</t>
+          <t>2533 - 1 - C</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5078,35 +5076,35 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>11/08/2026 14:47</t>
+          <t>11/08/2026 08:40</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>11/08/2026 14:58</t>
+          <t>11/08/2026 08:42</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>2721</v>
+        <v>2030</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="N34" s="2" t="n">
-        <v>46245.61597222222</v>
+        <v>46245.36111111111</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>46245.62361111111</v>
+        <v>46245.3625</v>
       </c>
       <c r="P34" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>46245</v>
@@ -5118,7 +5116,7 @@
         <v>32</v>
       </c>
       <c r="T34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U34" t="b">
         <v>0</v>
@@ -5139,7 +5137,7 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="AB34" t="b">
         <v>0</v>
@@ -5149,14 +5147,14 @@
       </c>
       <c r="AD34" t="inlineStr"/>
       <c r="AE34" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AF34" t="n">
-        <v>887</v>
+        <v>520</v>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="AH34" t="b">
@@ -5177,7 +5175,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>16849350</v>
+        <v>16852034</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -5186,22 +5184,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>415 - CENTRO 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Q032</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rua ROBERTO BUENO DA SILVA</t>
+          <t>Avenida BRASIL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>609 - R</t>
+          <t>2601 - R</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5216,35 +5214,35 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>11/08/2026 14:59</t>
+          <t>11/08/2026 08:42</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>11/08/2026 15:05</t>
+          <t>11/08/2026 08:44</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>2721</v>
+        <v>2030</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="N35" s="2" t="n">
-        <v>46245.62430555555</v>
+        <v>46245.3625</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>46245.62847222222</v>
+        <v>46245.36388888889</v>
       </c>
       <c r="P35" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>46245</v>
@@ -5256,7 +5254,7 @@
         <v>32</v>
       </c>
       <c r="T35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U35" t="b">
         <v>0</v>
@@ -5277,7 +5275,7 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>720</v>
+        <v>120</v>
       </c>
       <c r="AB35" t="b">
         <v>0</v>
@@ -5287,14 +5285,14 @@
       </c>
       <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AF35" t="n">
-        <v>899</v>
+        <v>522</v>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="AH35" t="b">
@@ -5315,7 +5313,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>16849351</v>
+        <v>16852035</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -5324,22 +5322,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>415 - CENTRO 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Q032</t>
+          <t>Q001</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rua ROBERTO BUENO DA SILVA</t>
+          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>597 - R</t>
+          <t>907 - 2 - R</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5354,35 +5352,35 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>11/08/2026 15:06</t>
+          <t>11/08/2026 08:59</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>11/08/2026 15:14</t>
+          <t>11/08/2026 09:01</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>2721</v>
+        <v>2030</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="N36" s="2" t="n">
-        <v>46245.62916666667</v>
+        <v>46245.37430555555</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>46245.63472222222</v>
+        <v>46245.37569444445</v>
       </c>
       <c r="P36" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>46245</v>
@@ -5394,7 +5392,7 @@
         <v>32</v>
       </c>
       <c r="T36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U36" t="b">
         <v>0</v>
@@ -5415,7 +5413,7 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>420</v>
+        <v>1020</v>
       </c>
       <c r="AB36" t="b">
         <v>0</v>
@@ -5425,14 +5423,14 @@
       </c>
       <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AF36" t="n">
-        <v>906</v>
+        <v>539</v>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="AH36" t="b">
@@ -5453,7 +5451,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>16849352</v>
+        <v>16852036</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -5462,22 +5460,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>415 - CENTRO 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Q032</t>
+          <t>Q001</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rua ROBERTO BUENO DA SILVA</t>
+          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>587 - R</t>
+          <t>907 - 1 - R</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5492,35 +5490,35 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>11/08/2026 15:16</t>
+          <t>11/08/2026 09:01</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>11/08/2026 15:24</t>
+          <t>11/08/2026 09:03</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>2721</v>
+        <v>2030</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="N37" s="2" t="n">
-        <v>46245.63611111111</v>
+        <v>46245.37569444445</v>
       </c>
       <c r="O37" s="2" t="n">
-        <v>46245.64166666667</v>
+        <v>46245.37708333333</v>
       </c>
       <c r="P37" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>46245</v>
@@ -5532,7 +5530,7 @@
         <v>32</v>
       </c>
       <c r="T37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U37" t="b">
         <v>0</v>
@@ -5553,7 +5551,7 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>600</v>
+        <v>120</v>
       </c>
       <c r="AB37" t="b">
         <v>0</v>
@@ -5563,14 +5561,14 @@
       </c>
       <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AF37" t="n">
-        <v>916</v>
+        <v>541</v>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="AH37" t="b">
@@ -5591,7 +5589,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>16849353</v>
+        <v>16852037</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -5600,22 +5598,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>415 - CENTRO 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Q032</t>
+          <t>Q001</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Avenida COSTA E SILVA</t>
+          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>573 - 1 - R</t>
+          <t>907 - R</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5630,35 +5628,35 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>11/08/2026 15:35</t>
+          <t>11/08/2026 09:03</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>11/08/2026 15:39</t>
+          <t>11/08/2026 09:04</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>2721</v>
+        <v>2030</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="N38" s="2" t="n">
-        <v>46245.64930555555</v>
+        <v>46245.37708333333</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>46245.65208333333</v>
+        <v>46245.37777777778</v>
       </c>
       <c r="P38" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>46245</v>
@@ -5670,7 +5668,7 @@
         <v>32</v>
       </c>
       <c r="T38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U38" t="b">
         <v>0</v>
@@ -5691,7 +5689,7 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1140</v>
+        <v>120</v>
       </c>
       <c r="AB38" t="b">
         <v>0</v>
@@ -5701,14 +5699,14 @@
       </c>
       <c r="AD38" t="inlineStr"/>
       <c r="AE38" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AF38" t="n">
-        <v>935</v>
+        <v>543</v>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="AH38" t="b">
@@ -5729,7 +5727,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>16849354</v>
+        <v>16852038</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -5738,22 +5736,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>415 - CENTRO 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Q032</t>
+          <t>Q001</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Avenida COSTA E SILVA</t>
+          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>570 - R</t>
+          <t>907 - 3 - R</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5768,35 +5766,35 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>11/08/2026 15:41</t>
+          <t>11/08/2026 09:04</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>11/08/2026 15:45</t>
+          <t>11/08/2026 09:05</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>2721</v>
+        <v>2030</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="N39" s="2" t="n">
-        <v>46245.65347222222</v>
+        <v>46245.37777777778</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>46245.65625</v>
+        <v>46245.37847222222</v>
       </c>
       <c r="P39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q39" s="3" t="n">
         <v>46245</v>
@@ -5808,7 +5806,7 @@
         <v>32</v>
       </c>
       <c r="T39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U39" t="b">
         <v>0</v>
@@ -5829,7 +5827,7 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>360</v>
+        <v>60</v>
       </c>
       <c r="AB39" t="b">
         <v>0</v>
@@ -5839,14 +5837,14 @@
       </c>
       <c r="AD39" t="inlineStr"/>
       <c r="AE39" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AF39" t="n">
-        <v>941</v>
+        <v>544</v>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="AH39" t="b">
@@ -5867,7 +5865,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>16849355</v>
+        <v>16849340</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -5881,17 +5879,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Q032</t>
+          <t>Q031</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Avenida COSTA E SILVA</t>
+          <t>Rua MONTEVIDEO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>582 - R</t>
+          <t>340 - R</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5906,12 +5904,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>11/08/2026 15:45</t>
+          <t>11/08/2026 13:52</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>11/08/2026 15:48</t>
+          <t>11/08/2026 13:56</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -5928,13 +5926,13 @@
         </is>
       </c>
       <c r="N40" s="2" t="n">
-        <v>46245.65625</v>
+        <v>46245.57777777778</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>46245.65833333333</v>
+        <v>46245.58055555556</v>
       </c>
       <c r="P40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q40" s="3" t="n">
         <v>46245</v>
@@ -5966,9 +5964,7 @@
       <c r="Z40" t="b">
         <v>0</v>
       </c>
-      <c r="AA40" t="n">
-        <v>240</v>
-      </c>
+      <c r="AA40" t="inlineStr"/>
       <c r="AB40" t="b">
         <v>0</v>
       </c>
@@ -5977,10 +5973,10 @@
       </c>
       <c r="AD40" t="inlineStr"/>
       <c r="AE40" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AF40" t="n">
-        <v>945</v>
+        <v>832</v>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
@@ -6005,7 +6001,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>16849356</v>
+        <v>16849341</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -6019,17 +6015,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Q032</t>
+          <t>Q031</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Avenida COSTA E SILVA</t>
+          <t>Rua MONTEVIDEO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>606 - C</t>
+          <t>340 - 1 - R</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -6044,12 +6040,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>11/08/2026 15:48</t>
+          <t>11/08/2026 13:56</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>11/08/2026 15:51</t>
+          <t>11/08/2026 14:01</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -6066,13 +6062,13 @@
         </is>
       </c>
       <c r="N41" s="2" t="n">
-        <v>46245.65833333333</v>
+        <v>46245.58055555556</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>46245.66041666667</v>
+        <v>46245.58402777778</v>
       </c>
       <c r="P41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q41" s="3" t="n">
         <v>46245</v>
@@ -6105,7 +6101,7 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="AB41" t="b">
         <v>0</v>
@@ -6115,10 +6111,10 @@
       </c>
       <c r="AD41" t="inlineStr"/>
       <c r="AE41" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AF41" t="n">
-        <v>948</v>
+        <v>836</v>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
@@ -6143,7 +6139,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>16849357</v>
+        <v>16849342</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -6157,17 +6153,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Q032</t>
+          <t>Q031</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Rua ROBERTO BUENO DA SILVA</t>
+          <t>Rua MONTEVIDEO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>573 - R</t>
+          <t>340 - 2 - R</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6182,12 +6178,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>11/08/2026 15:56</t>
+          <t>11/08/2026 14:02</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>11/08/2026 16:00</t>
+          <t>11/08/2026 14:05</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -6204,13 +6200,13 @@
         </is>
       </c>
       <c r="N42" s="2" t="n">
-        <v>46245.66388888889</v>
+        <v>46245.58472222222</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>46245.66666666666</v>
+        <v>46245.58680555555</v>
       </c>
       <c r="P42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q42" s="3" t="n">
         <v>46245</v>
@@ -6243,7 +6239,7 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>480</v>
+        <v>360</v>
       </c>
       <c r="AB42" t="b">
         <v>0</v>
@@ -6253,10 +6249,10 @@
       </c>
       <c r="AD42" t="inlineStr"/>
       <c r="AE42" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF42" t="n">
-        <v>956</v>
+        <v>842</v>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
@@ -6281,7 +6277,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>16849358</v>
+        <v>16849343</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -6295,17 +6291,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Q032</t>
+          <t>Q031</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rua ROBERTO BUENO DA SILVA</t>
+          <t>Rua MONTEVIDEO</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>621 - C</t>
+          <t>370 - R</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6320,12 +6316,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>11/08/2026 16:00</t>
+          <t>11/08/2026 14:06</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>11/08/2026 16:05</t>
+          <t>11/08/2026 14:10</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -6342,13 +6338,13 @@
         </is>
       </c>
       <c r="N43" s="2" t="n">
-        <v>46245.66666666666</v>
+        <v>46245.5875</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>46245.67013888889</v>
+        <v>46245.59027777778</v>
       </c>
       <c r="P43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>46245</v>
@@ -6391,29 +6387,2099 @@
       </c>
       <c r="AD43" t="inlineStr"/>
       <c r="AE43" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>846</v>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK43" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>16849344</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Rua MONTEVIDEO</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>400 - R</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>11/08/2026 14:14</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>11/08/2026 14:21</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>46245.59305555555</v>
+      </c>
+      <c r="O44" s="2" t="n">
+        <v>46245.59791666667</v>
+      </c>
+      <c r="P44" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q44" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R44" t="n">
+        <v>319</v>
+      </c>
+      <c r="S44" t="n">
+        <v>32</v>
+      </c>
+      <c r="T44" t="b">
+        <v>0</v>
+      </c>
+      <c r="U44" t="b">
+        <v>0</v>
+      </c>
+      <c r="V44" t="b">
+        <v>0</v>
+      </c>
+      <c r="W44" t="b">
+        <v>0</v>
+      </c>
+      <c r="X44" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>480</v>
+      </c>
+      <c r="AB44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>854</v>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL44" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>16849345</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Rua MONTEVIDEO</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>410 - OU</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>11/08/2026 14:21</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>11/08/2026 14:29</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="n">
+        <v>46245.59791666667</v>
+      </c>
+      <c r="O45" s="2" t="n">
+        <v>46245.60347222222</v>
+      </c>
+      <c r="P45" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R45" t="n">
+        <v>319</v>
+      </c>
+      <c r="S45" t="n">
+        <v>32</v>
+      </c>
+      <c r="T45" t="b">
+        <v>0</v>
+      </c>
+      <c r="U45" t="b">
+        <v>0</v>
+      </c>
+      <c r="V45" t="b">
+        <v>0</v>
+      </c>
+      <c r="W45" t="b">
+        <v>0</v>
+      </c>
+      <c r="X45" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>420</v>
+      </c>
+      <c r="AB45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>861</v>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL45" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>16849346</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Rua MONTEVIDEO</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>380 - OU</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>11/08/2026 14:29</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>11/08/2026 14:32</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>46245.60347222222</v>
+      </c>
+      <c r="O46" s="2" t="n">
+        <v>46245.60555555556</v>
+      </c>
+      <c r="P46" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R46" t="n">
+        <v>319</v>
+      </c>
+      <c r="S46" t="n">
+        <v>32</v>
+      </c>
+      <c r="T46" t="b">
+        <v>0</v>
+      </c>
+      <c r="U46" t="b">
+        <v>0</v>
+      </c>
+      <c r="V46" t="b">
+        <v>0</v>
+      </c>
+      <c r="W46" t="b">
+        <v>0</v>
+      </c>
+      <c r="X46" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>480</v>
+      </c>
+      <c r="AB46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>869</v>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL46" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>16849347</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Q030</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Rua MONTEVIDEO</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>01 - TB</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>11/08/2026 14:33</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>11/08/2026 14:40</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>46245.60625</v>
+      </c>
+      <c r="O47" s="2" t="n">
+        <v>46245.61111111111</v>
+      </c>
+      <c r="P47" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q47" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R47" t="n">
+        <v>319</v>
+      </c>
+      <c r="S47" t="n">
+        <v>32</v>
+      </c>
+      <c r="T47" t="b">
+        <v>0</v>
+      </c>
+      <c r="U47" t="b">
+        <v>0</v>
+      </c>
+      <c r="V47" t="b">
+        <v>0</v>
+      </c>
+      <c r="W47" t="b">
+        <v>0</v>
+      </c>
+      <c r="X47" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>873</v>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK47" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>16849348</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Rua ROBERTO BUENO DA SILVA</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>621 - 1 - R</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>11/08/2026 14:41</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>11/08/2026 14:47</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>46245.61180555556</v>
+      </c>
+      <c r="O48" s="2" t="n">
+        <v>46245.61597222222</v>
+      </c>
+      <c r="P48" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q48" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R48" t="n">
+        <v>319</v>
+      </c>
+      <c r="S48" t="n">
+        <v>32</v>
+      </c>
+      <c r="T48" t="b">
+        <v>0</v>
+      </c>
+      <c r="U48" t="b">
+        <v>0</v>
+      </c>
+      <c r="V48" t="b">
+        <v>0</v>
+      </c>
+      <c r="W48" t="b">
+        <v>0</v>
+      </c>
+      <c r="X48" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>480</v>
+      </c>
+      <c r="AB48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>881</v>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK48" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL48" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>16849349</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Rua ROBERTO BUENO DA SILVA</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>621 - 2 - TB</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>11/08/2026 14:47</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>11/08/2026 14:58</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>46245.61597222222</v>
+      </c>
+      <c r="O49" s="2" t="n">
+        <v>46245.62361111111</v>
+      </c>
+      <c r="P49" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q49" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R49" t="n">
+        <v>319</v>
+      </c>
+      <c r="S49" t="n">
+        <v>32</v>
+      </c>
+      <c r="T49" t="b">
+        <v>0</v>
+      </c>
+      <c r="U49" t="b">
+        <v>0</v>
+      </c>
+      <c r="V49" t="b">
+        <v>0</v>
+      </c>
+      <c r="W49" t="b">
+        <v>0</v>
+      </c>
+      <c r="X49" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>360</v>
+      </c>
+      <c r="AB49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>887</v>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK49" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL49" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>16849350</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Rua ROBERTO BUENO DA SILVA</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>609 - R</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>11/08/2026 14:59</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>11/08/2026 15:05</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>46245.62430555555</v>
+      </c>
+      <c r="O50" s="2" t="n">
+        <v>46245.62847222222</v>
+      </c>
+      <c r="P50" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q50" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R50" t="n">
+        <v>319</v>
+      </c>
+      <c r="S50" t="n">
+        <v>32</v>
+      </c>
+      <c r="T50" t="b">
+        <v>0</v>
+      </c>
+      <c r="U50" t="b">
+        <v>0</v>
+      </c>
+      <c r="V50" t="b">
+        <v>0</v>
+      </c>
+      <c r="W50" t="b">
+        <v>0</v>
+      </c>
+      <c r="X50" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>720</v>
+      </c>
+      <c r="AB50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>899</v>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK50" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>16849351</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Rua ROBERTO BUENO DA SILVA</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>597 - R</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>11/08/2026 15:06</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>11/08/2026 15:14</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="n">
+        <v>46245.62916666667</v>
+      </c>
+      <c r="O51" s="2" t="n">
+        <v>46245.63472222222</v>
+      </c>
+      <c r="P51" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q51" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R51" t="n">
+        <v>319</v>
+      </c>
+      <c r="S51" t="n">
+        <v>32</v>
+      </c>
+      <c r="T51" t="b">
+        <v>0</v>
+      </c>
+      <c r="U51" t="b">
+        <v>0</v>
+      </c>
+      <c r="V51" t="b">
+        <v>0</v>
+      </c>
+      <c r="W51" t="b">
+        <v>0</v>
+      </c>
+      <c r="X51" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>420</v>
+      </c>
+      <c r="AB51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>906</v>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK51" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>16849352</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Rua ROBERTO BUENO DA SILVA</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>587 - R</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>11/08/2026 15:16</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>11/08/2026 15:24</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>46245.63611111111</v>
+      </c>
+      <c r="O52" s="2" t="n">
+        <v>46245.64166666667</v>
+      </c>
+      <c r="P52" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q52" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R52" t="n">
+        <v>319</v>
+      </c>
+      <c r="S52" t="n">
+        <v>32</v>
+      </c>
+      <c r="T52" t="b">
+        <v>0</v>
+      </c>
+      <c r="U52" t="b">
+        <v>0</v>
+      </c>
+      <c r="V52" t="b">
+        <v>0</v>
+      </c>
+      <c r="W52" t="b">
+        <v>0</v>
+      </c>
+      <c r="X52" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>600</v>
+      </c>
+      <c r="AB52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>916</v>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK52" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>16849353</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Avenida COSTA E SILVA</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>573 - 1 - R</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>11/08/2026 15:35</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>11/08/2026 15:39</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="n">
+        <v>46245.64930555555</v>
+      </c>
+      <c r="O53" s="2" t="n">
+        <v>46245.65208333333</v>
+      </c>
+      <c r="P53" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q53" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R53" t="n">
+        <v>319</v>
+      </c>
+      <c r="S53" t="n">
+        <v>32</v>
+      </c>
+      <c r="T53" t="b">
+        <v>0</v>
+      </c>
+      <c r="U53" t="b">
+        <v>0</v>
+      </c>
+      <c r="V53" t="b">
+        <v>0</v>
+      </c>
+      <c r="W53" t="b">
+        <v>0</v>
+      </c>
+      <c r="X53" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>1140</v>
+      </c>
+      <c r="AB53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>935</v>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK53" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>16849354</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Avenida COSTA E SILVA</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>570 - R</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>11/08/2026 15:41</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>11/08/2026 15:45</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>46245.65347222222</v>
+      </c>
+      <c r="O54" s="2" t="n">
+        <v>46245.65625</v>
+      </c>
+      <c r="P54" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q54" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R54" t="n">
+        <v>319</v>
+      </c>
+      <c r="S54" t="n">
+        <v>32</v>
+      </c>
+      <c r="T54" t="b">
+        <v>0</v>
+      </c>
+      <c r="U54" t="b">
+        <v>0</v>
+      </c>
+      <c r="V54" t="b">
+        <v>0</v>
+      </c>
+      <c r="W54" t="b">
+        <v>0</v>
+      </c>
+      <c r="X54" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>360</v>
+      </c>
+      <c r="AB54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="inlineStr"/>
+      <c r="AE54" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>941</v>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK54" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>16849355</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Avenida COSTA E SILVA</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>582 - R</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>11/08/2026 15:45</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>11/08/2026 15:48</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v>46245.65625</v>
+      </c>
+      <c r="O55" s="2" t="n">
+        <v>46245.65833333333</v>
+      </c>
+      <c r="P55" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q55" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R55" t="n">
+        <v>319</v>
+      </c>
+      <c r="S55" t="n">
+        <v>32</v>
+      </c>
+      <c r="T55" t="b">
+        <v>0</v>
+      </c>
+      <c r="U55" t="b">
+        <v>0</v>
+      </c>
+      <c r="V55" t="b">
+        <v>0</v>
+      </c>
+      <c r="W55" t="b">
+        <v>0</v>
+      </c>
+      <c r="X55" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y55" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="inlineStr"/>
+      <c r="AE55" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>945</v>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK55" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>16849356</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Avenida COSTA E SILVA</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>606 - C</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>11/08/2026 15:48</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>11/08/2026 15:51</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="n">
+        <v>46245.65833333333</v>
+      </c>
+      <c r="O56" s="2" t="n">
+        <v>46245.66041666667</v>
+      </c>
+      <c r="P56" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q56" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R56" t="n">
+        <v>319</v>
+      </c>
+      <c r="S56" t="n">
+        <v>32</v>
+      </c>
+      <c r="T56" t="b">
+        <v>0</v>
+      </c>
+      <c r="U56" t="b">
+        <v>0</v>
+      </c>
+      <c r="V56" t="b">
+        <v>0</v>
+      </c>
+      <c r="W56" t="b">
+        <v>0</v>
+      </c>
+      <c r="X56" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD56" t="inlineStr"/>
+      <c r="AE56" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>948</v>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK56" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>16849357</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Rua ROBERTO BUENO DA SILVA</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>573 - R</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>11/08/2026 15:56</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>11/08/2026 16:00</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="n">
+        <v>46245.66388888889</v>
+      </c>
+      <c r="O57" s="2" t="n">
+        <v>46245.66666666666</v>
+      </c>
+      <c r="P57" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q57" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R57" t="n">
+        <v>319</v>
+      </c>
+      <c r="S57" t="n">
+        <v>32</v>
+      </c>
+      <c r="T57" t="b">
+        <v>0</v>
+      </c>
+      <c r="U57" t="b">
+        <v>0</v>
+      </c>
+      <c r="V57" t="b">
+        <v>0</v>
+      </c>
+      <c r="W57" t="b">
+        <v>0</v>
+      </c>
+      <c r="X57" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>480</v>
+      </c>
+      <c r="AB57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD57" t="inlineStr"/>
+      <c r="AE57" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>956</v>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK57" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>16849358</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Rua ROBERTO BUENO DA SILVA</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>621 - C</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Tratamento</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>11/08/2026 16:00</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>11/08/2026 16:05</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>2721</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="n">
+        <v>46245.66666666666</v>
+      </c>
+      <c r="O58" s="2" t="n">
+        <v>46245.67013888889</v>
+      </c>
+      <c r="P58" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q58" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="R58" t="n">
+        <v>319</v>
+      </c>
+      <c r="S58" t="n">
+        <v>32</v>
+      </c>
+      <c r="T58" t="b">
+        <v>0</v>
+      </c>
+      <c r="U58" t="b">
+        <v>0</v>
+      </c>
+      <c r="V58" t="b">
+        <v>0</v>
+      </c>
+      <c r="W58" t="b">
+        <v>0</v>
+      </c>
+      <c r="X58" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y58" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD58" t="inlineStr"/>
+      <c r="AE58" t="n">
         <v>16</v>
       </c>
-      <c r="AF43" t="n">
+      <c r="AF58" t="n">
         <v>960</v>
       </c>
-      <c r="AG43" t="inlineStr">
+      <c r="AG58" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="AH43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK43" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL43" t="b">
+      <c r="AH58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK58" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL58" t="b">
         <v>0</v>
       </c>
     </row>

--- a/data/semanas/319.xlsx
+++ b/data/semanas/319.xlsx
@@ -629,7 +629,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16828940</v>
+        <v>16850102</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -638,22 +638,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>405 - ALTOS DA GLÓRIA</t>
+          <t>409 - ANDREAZZA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Q012</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rua DR. MIGUEL MARCONDES ARMANDO</t>
+          <t>Rua DIGNO TORRES GIMENEZ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>926 - R</t>
+          <t>806 - R</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -663,25 +663,25 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Recuperação</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10/08/2026 15:27</t>
+          <t>11/08/2026 10:19</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10/08/2026 15:31</t>
+          <t>11/08/2026 10:21</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3037</v>
+        <v>3101</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Carlos Alberto Albiero</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -690,16 +690,16 @@
         </is>
       </c>
       <c r="N2" s="2" t="n">
-        <v>46244.64375</v>
+        <v>46245.42986111111</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>46244.64652777778</v>
+        <v>46245.43125</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="R2" t="n">
         <v>319</v>
@@ -708,7 +708,7 @@
         <v>32</v>
       </c>
       <c r="T2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
@@ -737,21 +737,21 @@
       </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AF2" t="n">
-        <v>927</v>
+        <v>619</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="AH2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ2" t="b">
         <v>0</v>
@@ -765,7 +765,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16828941</v>
+        <v>16847462</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -774,22 +774,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>405 - ALTOS DA GLÓRIA</t>
+          <t>408 - PARQUE DE EXPOSIÇÕES</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Q012</t>
+          <t>Q034</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rua RENE ZAMLUTTI</t>
+          <t>Rua DIGNO TORRES GIMENEZ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>355 - R</t>
+          <t>735 - R</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -804,20 +804,20 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10/08/2026 15:32</t>
+          <t>11/08/2026 09:56</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10/08/2026 15:35</t>
+          <t>11/08/2026 10:01</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>3037</v>
+        <v>30</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -826,16 +826,16 @@
         </is>
       </c>
       <c r="N3" s="2" t="n">
-        <v>46244.64722222222</v>
+        <v>46245.41388888889</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>46244.64930555555</v>
+        <v>46245.41736111111</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="R3" t="n">
         <v>319</v>
@@ -864,9 +864,7 @@
       <c r="Z3" t="b">
         <v>0</v>
       </c>
-      <c r="AA3" t="n">
-        <v>300</v>
-      </c>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="b">
         <v>0</v>
       </c>
@@ -875,21 +873,21 @@
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AF3" t="n">
-        <v>932</v>
+        <v>596</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="AH3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ3" t="b">
         <v>0</v>
@@ -903,7 +901,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>16828942</v>
+        <v>16847463</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -912,22 +910,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>405 - ALTOS DA GLÓRIA</t>
+          <t>408 - PARQUE DE EXPOSIÇÕES</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Q012</t>
+          <t>Q035</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rua RENE ZAMLUTTI</t>
+          <t>Rua DIGNO TORRES GIMENEZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>377 - R</t>
+          <t>718 - R</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -937,25 +935,25 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Recuperação</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10/08/2026 15:35</t>
+          <t>11/08/2026 10:02</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10/08/2026 15:38</t>
+          <t>11/08/2026 10:06</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>3037</v>
+        <v>30</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -964,16 +962,16 @@
         </is>
       </c>
       <c r="N4" s="2" t="n">
-        <v>46244.64930555555</v>
+        <v>46245.41805555556</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>46244.65138888889</v>
+        <v>46245.42083333333</v>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="R4" t="n">
         <v>319</v>
@@ -1003,7 +1001,7 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="AB4" t="b">
         <v>0</v>
@@ -1013,21 +1011,21 @@
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AF4" t="n">
-        <v>935</v>
+        <v>602</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="AH4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ4" t="b">
         <v>0</v>
@@ -1041,7 +1039,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>16828943</v>
+        <v>16847464</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1050,22 +1048,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>405 - ALTOS DA GLÓRIA</t>
+          <t>408 - PARQUE DE EXPOSIÇÕES</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Q001</t>
+          <t>Q034</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rua ELOAH VIEIRA DA SILVA</t>
+          <t>Rua DIGNO TORRES GIMENEZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>928 - R</t>
+          <t>713 - R</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1075,25 +1073,25 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Recuperação</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10/08/2026 15:41</t>
+          <t>11/08/2026 10:07</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>10/08/2026 15:47</t>
+          <t>11/08/2026 10:12</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>3037</v>
+        <v>30</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1102,16 +1100,16 @@
         </is>
       </c>
       <c r="N5" s="2" t="n">
-        <v>46244.65347222222</v>
+        <v>46245.42152777778</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>46244.65763888889</v>
+        <v>46245.425</v>
       </c>
       <c r="P5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="R5" t="n">
         <v>319</v>
@@ -1141,7 +1139,7 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="AB5" t="b">
         <v>0</v>
@@ -1151,21 +1149,21 @@
       </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AF5" t="n">
-        <v>941</v>
+        <v>607</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="AH5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ5" t="b">
         <v>0</v>
@@ -1179,7 +1177,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>16850102</v>
+        <v>16847465</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1188,12 +1186,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>409 - ANDREAZZA</t>
+          <t>408 - PARQUE DE EXPOSIÇÕES</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q034</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1203,7 +1201,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>806 - R</t>
+          <t>713 - 2 - R</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1213,25 +1211,25 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Recuperação</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>11/08/2026 10:19</t>
+          <t>11/08/2026 10:12</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11/08/2026 10:21</t>
+          <t>11/08/2026 10:15</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3101</v>
+        <v>30</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Carlos Alberto Albiero</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1240,13 +1238,13 @@
         </is>
       </c>
       <c r="N6" s="2" t="n">
-        <v>46245.42986111111</v>
+        <v>46245.425</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>46245.43125</v>
+        <v>46245.42708333334</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>46245</v>
@@ -1258,7 +1256,7 @@
         <v>32</v>
       </c>
       <c r="T6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
@@ -1278,7 +1276,9 @@
       <c r="Z6" t="b">
         <v>0</v>
       </c>
-      <c r="AA6" t="inlineStr"/>
+      <c r="AA6" t="n">
+        <v>300</v>
+      </c>
       <c r="AB6" t="b">
         <v>0</v>
       </c>
@@ -1290,7 +1290,7 @@
         <v>10</v>
       </c>
       <c r="AF6" t="n">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>16847462</v>
+        <v>16847466</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>735 - R</t>
+          <t>713 - 1 - R</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11/08/2026 09:56</t>
+          <t>11/08/2026 10:16</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11/08/2026 10:01</t>
+          <t>11/08/2026 10:23</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -1376,13 +1376,13 @@
         </is>
       </c>
       <c r="N7" s="2" t="n">
-        <v>46245.41388888889</v>
+        <v>46245.42777777778</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>46245.41736111111</v>
+        <v>46245.43263888889</v>
       </c>
       <c r="P7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>46245</v>
@@ -1414,7 +1414,9 @@
       <c r="Z7" t="b">
         <v>0</v>
       </c>
-      <c r="AA7" t="inlineStr"/>
+      <c r="AA7" t="n">
+        <v>240</v>
+      </c>
       <c r="AB7" t="b">
         <v>0</v>
       </c>
@@ -1423,10 +1425,10 @@
       </c>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF7" t="n">
-        <v>596</v>
+        <v>616</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
@@ -1451,7 +1453,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>16847463</v>
+        <v>16847467</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1465,7 +1467,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Q035</t>
+          <t>Q034</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1475,7 +1477,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>718 - R</t>
+          <t>701 - C</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1485,17 +1487,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Recuperação</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>11/08/2026 10:02</t>
+          <t>11/08/2026 10:23</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>11/08/2026 10:06</t>
+          <t>11/08/2026 10:26</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -1512,13 +1514,13 @@
         </is>
       </c>
       <c r="N8" s="2" t="n">
-        <v>46245.41805555556</v>
+        <v>46245.43263888889</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>46245.42083333333</v>
+        <v>46245.43472222222</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>46245</v>
@@ -1551,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="AB8" t="b">
         <v>0</v>
@@ -1564,7 +1566,7 @@
         <v>10</v>
       </c>
       <c r="AF8" t="n">
-        <v>602</v>
+        <v>623</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
@@ -1589,7 +1591,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>16847464</v>
+        <v>16847468</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1613,7 +1615,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>713 - R</t>
+          <t>701 - 1 - R</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1628,12 +1630,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>11/08/2026 10:07</t>
+          <t>11/08/2026 10:27</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>11/08/2026 10:12</t>
+          <t>11/08/2026 10:30</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1650,13 +1652,13 @@
         </is>
       </c>
       <c r="N9" s="2" t="n">
-        <v>46245.42152777778</v>
+        <v>46245.43541666667</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>46245.425</v>
+        <v>46245.4375</v>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>46245</v>
@@ -1689,7 +1691,7 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="AB9" t="b">
         <v>0</v>
@@ -1702,7 +1704,7 @@
         <v>10</v>
       </c>
       <c r="AF9" t="n">
-        <v>607</v>
+        <v>627</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
@@ -1727,7 +1729,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>16847465</v>
+        <v>16847471</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1751,7 +1753,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>713 - 2 - R</t>
+          <t>689 - R</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1766,12 +1768,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>11/08/2026 10:12</t>
+          <t>11/08/2026 10:30</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>11/08/2026 10:15</t>
+          <t>11/08/2026 10:38</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1788,13 +1790,13 @@
         </is>
       </c>
       <c r="N10" s="2" t="n">
-        <v>46245.425</v>
+        <v>46245.4375</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>46245.42708333334</v>
+        <v>46245.44305555556</v>
       </c>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>46245</v>
@@ -1827,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>300</v>
+        <v>180</v>
       </c>
       <c r="AB10" t="b">
         <v>0</v>
@@ -1840,7 +1842,7 @@
         <v>10</v>
       </c>
       <c r="AF10" t="n">
-        <v>612</v>
+        <v>630</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
@@ -1865,7 +1867,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>16847466</v>
+        <v>16847472</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1889,7 +1891,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>713 - 1 - R</t>
+          <t>653 - C</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1904,12 +1906,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>11/08/2026 10:16</t>
+          <t>11/08/2026 10:38</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>11/08/2026 10:23</t>
+          <t>11/08/2026 10:44</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1926,13 +1928,13 @@
         </is>
       </c>
       <c r="N11" s="2" t="n">
-        <v>46245.42777777778</v>
+        <v>46245.44305555556</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>46245.43263888889</v>
+        <v>46245.44722222222</v>
       </c>
       <c r="P11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>46245</v>
@@ -1965,7 +1967,7 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>240</v>
+        <v>480</v>
       </c>
       <c r="AB11" t="b">
         <v>0</v>
@@ -1978,7 +1980,7 @@
         <v>10</v>
       </c>
       <c r="AF11" t="n">
-        <v>616</v>
+        <v>638</v>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
@@ -2003,7 +2005,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>16847467</v>
+        <v>16847473</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2027,7 +2029,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>701 - C</t>
+          <t>653 - 1 - C</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2042,12 +2044,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>11/08/2026 10:23</t>
+          <t>11/08/2026 10:44</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>11/08/2026 10:26</t>
+          <t>11/08/2026 10:47</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -2064,10 +2066,10 @@
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>46245.43263888889</v>
+        <v>46245.44722222222</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>46245.43472222222</v>
+        <v>46245.44930555556</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -2103,7 +2105,7 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>420</v>
+        <v>360</v>
       </c>
       <c r="AB12" t="b">
         <v>0</v>
@@ -2116,7 +2118,7 @@
         <v>10</v>
       </c>
       <c r="AF12" t="n">
-        <v>623</v>
+        <v>644</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
@@ -2141,7 +2143,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>16847468</v>
+        <v>16847474</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -2165,7 +2167,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>701 - 1 - R</t>
+          <t>653 - 2 - C</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2180,12 +2182,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>11/08/2026 10:27</t>
+          <t>11/08/2026 10:48</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>11/08/2026 10:30</t>
+          <t>11/08/2026 10:51</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -2202,10 +2204,10 @@
         </is>
       </c>
       <c r="N13" s="2" t="n">
-        <v>46245.43541666667</v>
+        <v>46245.45</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>46245.4375</v>
+        <v>46245.45208333333</v>
       </c>
       <c r="P13" t="n">
         <v>3</v>
@@ -2254,7 +2256,7 @@
         <v>10</v>
       </c>
       <c r="AF13" t="n">
-        <v>627</v>
+        <v>648</v>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
@@ -2279,7 +2281,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>16847471</v>
+        <v>16847475</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2303,7 +2305,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>689 - R</t>
+          <t>653 - 3 - C</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2318,12 +2320,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>11/08/2026 10:30</t>
+          <t>11/08/2026 10:51</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>11/08/2026 10:38</t>
+          <t>11/08/2026 10:55</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -2340,13 +2342,13 @@
         </is>
       </c>
       <c r="N14" s="2" t="n">
-        <v>46245.4375</v>
+        <v>46245.45208333333</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>46245.44305555556</v>
+        <v>46245.45486111111</v>
       </c>
       <c r="P14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>46245</v>
@@ -2392,7 +2394,7 @@
         <v>10</v>
       </c>
       <c r="AF14" t="n">
-        <v>630</v>
+        <v>651</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
@@ -2417,7 +2419,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>16847472</v>
+        <v>16847476</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2441,7 +2443,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>653 - C</t>
+          <t>653 - 4 - C</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2456,12 +2458,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>11/08/2026 10:38</t>
+          <t>11/08/2026 10:55</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>11/08/2026 10:44</t>
+          <t>11/08/2026 10:59</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -2478,13 +2480,13 @@
         </is>
       </c>
       <c r="N15" s="2" t="n">
-        <v>46245.44305555556</v>
+        <v>46245.45486111111</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>46245.44722222222</v>
+        <v>46245.45763888889</v>
       </c>
       <c r="P15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>46245</v>
@@ -2517,7 +2519,7 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>480</v>
+        <v>240</v>
       </c>
       <c r="AB15" t="b">
         <v>0</v>
@@ -2530,7 +2532,7 @@
         <v>10</v>
       </c>
       <c r="AF15" t="n">
-        <v>638</v>
+        <v>655</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
@@ -2555,7 +2557,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>16847473</v>
+        <v>16847477</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2569,17 +2571,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Q034</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rua DIGNO TORRES GIMENEZ</t>
+          <t>Rua CORONEL PONCE</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>653 - 1 - C</t>
+          <t>562 - R</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2589,17 +2591,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Recuperação</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>11/08/2026 10:44</t>
+          <t>11/08/2026 12:55</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>11/08/2026 10:47</t>
+          <t>11/08/2026 12:58</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -2616,10 +2618,10 @@
         </is>
       </c>
       <c r="N16" s="2" t="n">
-        <v>46245.44722222222</v>
+        <v>46245.53819444445</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>46245.44930555556</v>
+        <v>46245.54027777778</v>
       </c>
       <c r="P16" t="n">
         <v>3</v>
@@ -2655,7 +2657,7 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>360</v>
+        <v>7200</v>
       </c>
       <c r="AB16" t="b">
         <v>0</v>
@@ -2665,14 +2667,14 @@
       </c>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AF16" t="n">
-        <v>644</v>
+        <v>775</v>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="AH16" t="b">
@@ -2685,15 +2687,15 @@
         <v>0</v>
       </c>
       <c r="AK16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16847474</v>
+        <v>16847480</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2712,12 +2714,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rua DIGNO TORRES GIMENEZ</t>
+          <t>Rua RAUL PEREIRA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>653 - 2 - C</t>
+          <t>653 - 7 - OU</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2732,12 +2734,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>11/08/2026 10:48</t>
+          <t>11/08/2026 13:09</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>11/08/2026 10:51</t>
+          <t>11/08/2026 13:13</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -2754,13 +2756,13 @@
         </is>
       </c>
       <c r="N17" s="2" t="n">
-        <v>46245.45</v>
+        <v>46245.54791666667</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>46245.45208333333</v>
+        <v>46245.55069444444</v>
       </c>
       <c r="P17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>46245</v>
@@ -2793,7 +2795,7 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>240</v>
+        <v>840</v>
       </c>
       <c r="AB17" t="b">
         <v>0</v>
@@ -2803,14 +2805,14 @@
       </c>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AF17" t="n">
-        <v>648</v>
+        <v>789</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="AH17" t="b">
@@ -2831,7 +2833,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>16847475</v>
+        <v>16847481</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2850,12 +2852,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rua DIGNO TORRES GIMENEZ</t>
+          <t>Rua RAUL PEREIRA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>653 - 3 - C</t>
+          <t>653 - 8 - OU</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2870,12 +2872,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>11/08/2026 10:51</t>
+          <t>11/08/2026 13:13</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>11/08/2026 10:55</t>
+          <t>11/08/2026 13:18</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -2892,13 +2894,13 @@
         </is>
       </c>
       <c r="N18" s="2" t="n">
-        <v>46245.45208333333</v>
+        <v>46245.55069444444</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>46245.45486111111</v>
+        <v>46245.55416666667</v>
       </c>
       <c r="P18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q18" s="3" t="n">
         <v>46245</v>
@@ -2931,7 +2933,7 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="AB18" t="b">
         <v>0</v>
@@ -2941,14 +2943,14 @@
       </c>
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AF18" t="n">
-        <v>651</v>
+        <v>793</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="AH18" t="b">
@@ -2969,7 +2971,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>16847476</v>
+        <v>16847482</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2988,12 +2990,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rua DIGNO TORRES GIMENEZ</t>
+          <t>Rua RAUL PEREIRA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>653 - 4 - C</t>
+          <t>653 - 9 - OU</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -3008,12 +3010,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>11/08/2026 10:55</t>
+          <t>11/08/2026 13:18</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>11/08/2026 10:59</t>
+          <t>11/08/2026 13:22</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -3030,10 +3032,10 @@
         </is>
       </c>
       <c r="N19" s="2" t="n">
-        <v>46245.45486111111</v>
+        <v>46245.55416666667</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>46245.45763888889</v>
+        <v>46245.55694444444</v>
       </c>
       <c r="P19" t="n">
         <v>4</v>
@@ -3069,7 +3071,7 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="AB19" t="b">
         <v>0</v>
@@ -3079,14 +3081,14 @@
       </c>
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AF19" t="n">
-        <v>655</v>
+        <v>798</v>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="AH19" t="b">
@@ -3107,7 +3109,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>16847477</v>
+        <v>16847483</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -3121,17 +3123,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Q019</t>
+          <t>Q034</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rua CORONEL PONCE</t>
+          <t>Rua RAUL PEREIRA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>562 - R</t>
+          <t>653 - 10 - OU</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3141,17 +3143,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Recuperação</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>11/08/2026 12:55</t>
+          <t>11/08/2026 13:22</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>11/08/2026 12:58</t>
+          <t>11/08/2026 13:27</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -3168,13 +3170,13 @@
         </is>
       </c>
       <c r="N20" s="2" t="n">
-        <v>46245.53819444445</v>
+        <v>46245.55694444444</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>46245.54027777778</v>
+        <v>46245.56041666667</v>
       </c>
       <c r="P20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>46245</v>
@@ -3207,7 +3209,7 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>7200</v>
+        <v>240</v>
       </c>
       <c r="AB20" t="b">
         <v>0</v>
@@ -3217,10 +3219,10 @@
       </c>
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF20" t="n">
-        <v>775</v>
+        <v>802</v>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
@@ -3237,15 +3239,15 @@
         <v>0</v>
       </c>
       <c r="AK20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>16847480</v>
+        <v>16847484</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -3269,7 +3271,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>653 - 7 - OU</t>
+          <t>653 - 11 - OU</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3284,12 +3286,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>11/08/2026 13:09</t>
+          <t>11/08/2026 13:27</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>11/08/2026 13:13</t>
+          <t>11/08/2026 13:29</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -3306,13 +3308,13 @@
         </is>
       </c>
       <c r="N21" s="2" t="n">
-        <v>46245.54791666667</v>
+        <v>46245.56041666667</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>46245.55069444444</v>
+        <v>46245.56180555555</v>
       </c>
       <c r="P21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>46245</v>
@@ -3324,7 +3326,7 @@
         <v>32</v>
       </c>
       <c r="T21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U21" t="b">
         <v>0</v>
@@ -3345,7 +3347,7 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>840</v>
+        <v>300</v>
       </c>
       <c r="AB21" t="b">
         <v>0</v>
@@ -3358,7 +3360,7 @@
         <v>13</v>
       </c>
       <c r="AF21" t="n">
-        <v>789</v>
+        <v>807</v>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
@@ -3383,7 +3385,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>16847481</v>
+        <v>16852016</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -3392,22 +3394,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>408 - PARQUE DE EXPOSIÇÕES</t>
+          <t>415 - CENTRO 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Q034</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rua RAUL PEREIRA</t>
+          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>653 - 8 - OU</t>
+          <t>1484 - 4 - R - 104</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3422,35 +3424,35 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>11/08/2026 13:13</t>
+          <t>11/08/2026 08:05</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>11/08/2026 13:18</t>
+          <t>11/08/2026 08:08</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>30</v>
+        <v>2030</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="N22" s="2" t="n">
-        <v>46245.55069444444</v>
+        <v>46245.33680555555</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>46245.55416666667</v>
+        <v>46245.33888888889</v>
       </c>
       <c r="P22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>46245</v>
@@ -3482,9 +3484,7 @@
       <c r="Z22" t="b">
         <v>0</v>
       </c>
-      <c r="AA22" t="n">
-        <v>240</v>
-      </c>
+      <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="b">
         <v>0</v>
       </c>
@@ -3493,14 +3493,14 @@
       </c>
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AF22" t="n">
-        <v>793</v>
+        <v>485</v>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="AH22" t="b">
@@ -3521,7 +3521,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>16847482</v>
+        <v>16852018</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3530,22 +3530,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>408 - PARQUE DE EXPOSIÇÕES</t>
+          <t>415 - CENTRO 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Q034</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rua RAUL PEREIRA</t>
+          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>653 - 9 - OU</t>
+          <t>1484 - 5 - R</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3560,32 +3560,32 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>11/08/2026 13:18</t>
+          <t>11/08/2026 08:08</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>11/08/2026 13:22</t>
+          <t>11/08/2026 08:12</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>30</v>
+        <v>2030</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="N23" s="2" t="n">
-        <v>46245.55416666667</v>
+        <v>46245.33888888889</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>46245.55694444444</v>
+        <v>46245.34166666667</v>
       </c>
       <c r="P23" t="n">
         <v>4</v>
@@ -3621,7 +3621,7 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>300</v>
+        <v>180</v>
       </c>
       <c r="AB23" t="b">
         <v>0</v>
@@ -3631,14 +3631,14 @@
       </c>
       <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AF23" t="n">
-        <v>798</v>
+        <v>488</v>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="AH23" t="b">
@@ -3659,7 +3659,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>16847483</v>
+        <v>16852020</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3668,22 +3668,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>408 - PARQUE DE EXPOSIÇÕES</t>
+          <t>415 - CENTRO 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Q034</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rua RAUL PEREIRA</t>
+          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>653 - 10 - OU</t>
+          <t>1469 - 1 - C</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3698,35 +3698,35 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>11/08/2026 13:22</t>
+          <t>11/08/2026 08:12</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>11/08/2026 13:27</t>
+          <t>11/08/2026 08:15</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>30</v>
+        <v>2030</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="N24" s="2" t="n">
-        <v>46245.55694444444</v>
+        <v>46245.34166666667</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>46245.56041666667</v>
+        <v>46245.34375</v>
       </c>
       <c r="P24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>46245</v>
@@ -3769,14 +3769,14 @@
       </c>
       <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AF24" t="n">
-        <v>802</v>
+        <v>492</v>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="AH24" t="b">
@@ -3797,7 +3797,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>16847484</v>
+        <v>16852023</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>408 - PARQUE DE EXPOSIÇÕES</t>
+          <t>415 - CENTRO 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Q034</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rua RAUL PEREIRA</t>
+          <t>Rua PARAGUAI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>653 - 11 - OU</t>
+          <t>2568 - R</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3836,35 +3836,35 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>11/08/2026 13:27</t>
+          <t>11/08/2026 08:16</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>11/08/2026 13:29</t>
+          <t>11/08/2026 08:20</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>30</v>
+        <v>2030</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="N25" s="2" t="n">
-        <v>46245.56041666667</v>
+        <v>46245.34444444445</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>46245.56180555555</v>
+        <v>46245.34722222222</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q25" s="3" t="n">
         <v>46245</v>
@@ -3876,7 +3876,7 @@
         <v>32</v>
       </c>
       <c r="T25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U25" t="b">
         <v>0</v>
@@ -3897,7 +3897,7 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="AB25" t="b">
         <v>0</v>
@@ -3907,14 +3907,14 @@
       </c>
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AF25" t="n">
-        <v>807</v>
+        <v>496</v>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="AH25" t="b">
@@ -3935,7 +3935,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>16852016</v>
+        <v>16852027</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3954,12 +3954,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
+          <t>Rua PARAGUAI</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1484 - 4 - R - 104</t>
+          <t>2598 - OU</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>11/08/2026 08:05</t>
+          <t>11/08/2026 08:20</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>11/08/2026 08:08</t>
+          <t>11/08/2026 08:25</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -3996,13 +3996,13 @@
         </is>
       </c>
       <c r="N26" s="2" t="n">
-        <v>46245.33680555555</v>
+        <v>46245.34722222222</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>46245.33888888889</v>
+        <v>46245.35069444445</v>
       </c>
       <c r="P26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>46245</v>
@@ -4034,7 +4034,9 @@
       <c r="Z26" t="b">
         <v>0</v>
       </c>
-      <c r="AA26" t="inlineStr"/>
+      <c r="AA26" t="n">
+        <v>240</v>
+      </c>
       <c r="AB26" t="b">
         <v>0</v>
       </c>
@@ -4046,7 +4048,7 @@
         <v>8</v>
       </c>
       <c r="AF26" t="n">
-        <v>485</v>
+        <v>500</v>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
@@ -4071,7 +4073,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>16852018</v>
+        <v>16852030</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -4085,17 +4087,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Q010</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
+          <t>Rua GUIA LOPES</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1484 - 5 - R</t>
+          <t>278 - C</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4110,12 +4112,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>11/08/2026 08:08</t>
+          <t>11/08/2026 08:28</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>11/08/2026 08:12</t>
+          <t>11/08/2026 08:31</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -4132,13 +4134,13 @@
         </is>
       </c>
       <c r="N27" s="2" t="n">
-        <v>46245.33888888889</v>
+        <v>46245.35277777778</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>46245.34166666667</v>
+        <v>46245.35486111111</v>
       </c>
       <c r="P27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>46245</v>
@@ -4171,7 +4173,7 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>180</v>
+        <v>480</v>
       </c>
       <c r="AB27" t="b">
         <v>0</v>
@@ -4184,7 +4186,7 @@
         <v>8</v>
       </c>
       <c r="AF27" t="n">
-        <v>488</v>
+        <v>508</v>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
@@ -4209,7 +4211,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>16852020</v>
+        <v>16852031</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -4223,17 +4225,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Q010</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
+          <t>Rua GUIA LOPES</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1469 - 1 - C</t>
+          <t>146 - C</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4248,12 +4250,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>11/08/2026 08:12</t>
+          <t>11/08/2026 08:31</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>11/08/2026 08:15</t>
+          <t>11/08/2026 08:33</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -4270,13 +4272,13 @@
         </is>
       </c>
       <c r="N28" s="2" t="n">
-        <v>46245.34166666667</v>
+        <v>46245.35486111111</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>46245.34375</v>
+        <v>46245.35625</v>
       </c>
       <c r="P28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>46245</v>
@@ -4288,7 +4290,7 @@
         <v>32</v>
       </c>
       <c r="T28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U28" t="b">
         <v>0</v>
@@ -4309,7 +4311,7 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="AB28" t="b">
         <v>0</v>
@@ -4322,7 +4324,7 @@
         <v>8</v>
       </c>
       <c r="AF28" t="n">
-        <v>492</v>
+        <v>511</v>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
@@ -4347,7 +4349,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>16852023</v>
+        <v>16852032</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -4361,17 +4363,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Q010</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rua PARAGUAI</t>
+          <t>Avenida BRASIL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2568 - R</t>
+          <t>2485 - R</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4386,12 +4388,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>11/08/2026 08:16</t>
+          <t>11/08/2026 08:35</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>11/08/2026 08:20</t>
+          <t>11/08/2026 08:40</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -4408,13 +4410,13 @@
         </is>
       </c>
       <c r="N29" s="2" t="n">
-        <v>46245.34444444445</v>
+        <v>46245.35763888889</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>46245.34722222222</v>
+        <v>46245.36111111111</v>
       </c>
       <c r="P29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>46245</v>
@@ -4460,7 +4462,7 @@
         <v>8</v>
       </c>
       <c r="AF29" t="n">
-        <v>496</v>
+        <v>515</v>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
@@ -4485,7 +4487,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>16852027</v>
+        <v>16852033</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -4499,17 +4501,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Q010</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rua PARAGUAI</t>
+          <t>Avenida BRASIL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2598 - OU</t>
+          <t>2533 - 1 - C</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4524,12 +4526,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>11/08/2026 08:20</t>
+          <t>11/08/2026 08:40</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>11/08/2026 08:25</t>
+          <t>11/08/2026 08:42</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -4546,13 +4548,13 @@
         </is>
       </c>
       <c r="N30" s="2" t="n">
-        <v>46245.34722222222</v>
+        <v>46245.36111111111</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>46245.35069444445</v>
+        <v>46245.3625</v>
       </c>
       <c r="P30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>46245</v>
@@ -4564,7 +4566,7 @@
         <v>32</v>
       </c>
       <c r="T30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U30" t="b">
         <v>0</v>
@@ -4585,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="AB30" t="b">
         <v>0</v>
@@ -4598,7 +4600,7 @@
         <v>8</v>
       </c>
       <c r="AF30" t="n">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
@@ -4623,7 +4625,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>16852030</v>
+        <v>16852034</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -4642,12 +4644,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rua GUIA LOPES</t>
+          <t>Avenida BRASIL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>278 - C</t>
+          <t>2601 - R</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4662,12 +4664,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>11/08/2026 08:28</t>
+          <t>11/08/2026 08:42</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>11/08/2026 08:31</t>
+          <t>11/08/2026 08:44</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -4684,13 +4686,13 @@
         </is>
       </c>
       <c r="N31" s="2" t="n">
-        <v>46245.35277777778</v>
+        <v>46245.3625</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>46245.35486111111</v>
+        <v>46245.36388888889</v>
       </c>
       <c r="P31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>46245</v>
@@ -4702,7 +4704,7 @@
         <v>32</v>
       </c>
       <c r="T31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U31" t="b">
         <v>0</v>
@@ -4723,7 +4725,7 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="AB31" t="b">
         <v>0</v>
@@ -4736,7 +4738,7 @@
         <v>8</v>
       </c>
       <c r="AF31" t="n">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
@@ -4761,7 +4763,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>16852031</v>
+        <v>16852035</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4775,17 +4777,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q001</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rua GUIA LOPES</t>
+          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>146 - C</t>
+          <t>907 - 2 - R</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4800,12 +4802,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>11/08/2026 08:31</t>
+          <t>11/08/2026 08:59</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>11/08/2026 08:33</t>
+          <t>11/08/2026 09:01</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -4822,10 +4824,10 @@
         </is>
       </c>
       <c r="N32" s="2" t="n">
-        <v>46245.35486111111</v>
+        <v>46245.37430555555</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>46245.35625</v>
+        <v>46245.37569444445</v>
       </c>
       <c r="P32" t="n">
         <v>2</v>
@@ -4861,7 +4863,7 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>180</v>
+        <v>1020</v>
       </c>
       <c r="AB32" t="b">
         <v>0</v>
@@ -4874,7 +4876,7 @@
         <v>8</v>
       </c>
       <c r="AF32" t="n">
-        <v>511</v>
+        <v>539</v>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
@@ -4899,7 +4901,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>16852032</v>
+        <v>16852036</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4913,17 +4915,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q001</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Avenida BRASIL</t>
+          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2485 - R</t>
+          <t>907 - 1 - R</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4938,12 +4940,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>11/08/2026 08:35</t>
+          <t>11/08/2026 09:01</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>11/08/2026 08:40</t>
+          <t>11/08/2026 09:03</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -4960,13 +4962,13 @@
         </is>
       </c>
       <c r="N33" s="2" t="n">
-        <v>46245.35763888889</v>
+        <v>46245.37569444445</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>46245.36111111111</v>
+        <v>46245.37708333333</v>
       </c>
       <c r="P33" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q33" s="3" t="n">
         <v>46245</v>
@@ -4978,7 +4980,7 @@
         <v>32</v>
       </c>
       <c r="T33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U33" t="b">
         <v>0</v>
@@ -4999,7 +5001,7 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="AB33" t="b">
         <v>0</v>
@@ -5009,10 +5011,10 @@
       </c>
       <c r="AD33" t="inlineStr"/>
       <c r="AE33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF33" t="n">
-        <v>515</v>
+        <v>541</v>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
@@ -5037,7 +5039,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>16852033</v>
+        <v>16852037</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -5051,17 +5053,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q001</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Avenida BRASIL</t>
+          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2533 - 1 - C</t>
+          <t>907 - R</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5076,12 +5078,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>11/08/2026 08:40</t>
+          <t>11/08/2026 09:03</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>11/08/2026 08:42</t>
+          <t>11/08/2026 09:04</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -5098,13 +5100,13 @@
         </is>
       </c>
       <c r="N34" s="2" t="n">
-        <v>46245.36111111111</v>
+        <v>46245.37708333333</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>46245.3625</v>
+        <v>46245.37777777778</v>
       </c>
       <c r="P34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>46245</v>
@@ -5137,7 +5139,7 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="AB34" t="b">
         <v>0</v>
@@ -5147,10 +5149,10 @@
       </c>
       <c r="AD34" t="inlineStr"/>
       <c r="AE34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF34" t="n">
-        <v>520</v>
+        <v>543</v>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
@@ -5175,7 +5177,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>16852034</v>
+        <v>16852038</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -5189,17 +5191,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q001</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Avenida BRASIL</t>
+          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2601 - R</t>
+          <t>907 - 3 - R</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5214,12 +5216,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>11/08/2026 08:42</t>
+          <t>11/08/2026 09:04</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>11/08/2026 08:44</t>
+          <t>11/08/2026 09:05</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -5236,13 +5238,13 @@
         </is>
       </c>
       <c r="N35" s="2" t="n">
-        <v>46245.3625</v>
+        <v>46245.37777777778</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>46245.36388888889</v>
+        <v>46245.37847222222</v>
       </c>
       <c r="P35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>46245</v>
@@ -5275,7 +5277,7 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AB35" t="b">
         <v>0</v>
@@ -5285,10 +5287,10 @@
       </c>
       <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF35" t="n">
-        <v>522</v>
+        <v>544</v>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
@@ -5313,7 +5315,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>16852035</v>
+        <v>16849340</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -5322,22 +5324,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>415 - CENTRO 1</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Q001</t>
+          <t>Q031</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
+          <t>Rua MONTEVIDEO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>907 - 2 - R</t>
+          <t>340 - R</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5352,35 +5354,35 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>11/08/2026 08:59</t>
+          <t>11/08/2026 13:52</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>11/08/2026 09:01</t>
+          <t>11/08/2026 13:56</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>2030</v>
+        <v>2721</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Mateus Falcao de Souza</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="N36" s="2" t="n">
-        <v>46245.37430555555</v>
+        <v>46245.57777777778</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>46245.37569444445</v>
+        <v>46245.58055555556</v>
       </c>
       <c r="P36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>46245</v>
@@ -5392,7 +5394,7 @@
         <v>32</v>
       </c>
       <c r="T36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U36" t="b">
         <v>0</v>
@@ -5412,9 +5414,7 @@
       <c r="Z36" t="b">
         <v>0</v>
       </c>
-      <c r="AA36" t="n">
-        <v>1020</v>
-      </c>
+      <c r="AA36" t="inlineStr"/>
       <c r="AB36" t="b">
         <v>0</v>
       </c>
@@ -5423,14 +5423,14 @@
       </c>
       <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AF36" t="n">
-        <v>539</v>
+        <v>832</v>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="AH36" t="b">
@@ -5451,7 +5451,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>16852036</v>
+        <v>16849341</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -5460,22 +5460,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>415 - CENTRO 1</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Q001</t>
+          <t>Q031</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
+          <t>Rua MONTEVIDEO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>907 - 1 - R</t>
+          <t>340 - 1 - R</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5490,35 +5490,35 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>11/08/2026 09:01</t>
+          <t>11/08/2026 13:56</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>11/08/2026 09:03</t>
+          <t>11/08/2026 14:01</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>2030</v>
+        <v>2721</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Mateus Falcao de Souza</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="N37" s="2" t="n">
-        <v>46245.37569444445</v>
+        <v>46245.58055555556</v>
       </c>
       <c r="O37" s="2" t="n">
-        <v>46245.37708333333</v>
+        <v>46245.58402777778</v>
       </c>
       <c r="P37" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>46245</v>
@@ -5530,7 +5530,7 @@
         <v>32</v>
       </c>
       <c r="T37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U37" t="b">
         <v>0</v>
@@ -5551,7 +5551,7 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="AB37" t="b">
         <v>0</v>
@@ -5561,14 +5561,14 @@
       </c>
       <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AF37" t="n">
-        <v>541</v>
+        <v>836</v>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="AH37" t="b">
@@ -5589,7 +5589,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>16852037</v>
+        <v>16849342</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -5598,22 +5598,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>415 - CENTRO 1</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Q001</t>
+          <t>Q031</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
+          <t>Rua MONTEVIDEO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>907 - R</t>
+          <t>340 - 2 - R</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5628,35 +5628,35 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>11/08/2026 09:03</t>
+          <t>11/08/2026 14:02</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>11/08/2026 09:04</t>
+          <t>11/08/2026 14:05</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>2030</v>
+        <v>2721</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Mateus Falcao de Souza</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="N38" s="2" t="n">
-        <v>46245.37708333333</v>
+        <v>46245.58472222222</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>46245.37777777778</v>
+        <v>46245.58680555555</v>
       </c>
       <c r="P38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>46245</v>
@@ -5668,7 +5668,7 @@
         <v>32</v>
       </c>
       <c r="T38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U38" t="b">
         <v>0</v>
@@ -5689,7 +5689,7 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>120</v>
+        <v>360</v>
       </c>
       <c r="AB38" t="b">
         <v>0</v>
@@ -5699,14 +5699,14 @@
       </c>
       <c r="AD38" t="inlineStr"/>
       <c r="AE38" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AF38" t="n">
-        <v>543</v>
+        <v>842</v>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="AH38" t="b">
@@ -5727,7 +5727,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>16852038</v>
+        <v>16849343</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -5736,22 +5736,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>415 - CENTRO 1</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Q001</t>
+          <t>Q031</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
+          <t>Rua MONTEVIDEO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>907 - 3 - R</t>
+          <t>370 - R</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5766,35 +5766,35 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>11/08/2026 09:04</t>
+          <t>11/08/2026 14:06</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>11/08/2026 09:05</t>
+          <t>11/08/2026 14:10</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>2030</v>
+        <v>2721</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Mateus Falcao de Souza</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="N39" s="2" t="n">
-        <v>46245.37777777778</v>
+        <v>46245.5875</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>46245.37847222222</v>
+        <v>46245.59027777778</v>
       </c>
       <c r="P39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q39" s="3" t="n">
         <v>46245</v>
@@ -5806,7 +5806,7 @@
         <v>32</v>
       </c>
       <c r="T39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U39" t="b">
         <v>0</v>
@@ -5827,7 +5827,7 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="AB39" t="b">
         <v>0</v>
@@ -5837,14 +5837,14 @@
       </c>
       <c r="AD39" t="inlineStr"/>
       <c r="AE39" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AF39" t="n">
-        <v>544</v>
+        <v>846</v>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="AH39" t="b">
@@ -5865,7 +5865,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>16849340</v>
+        <v>16849344</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>340 - R</t>
+          <t>400 - R</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>11/08/2026 13:52</t>
+          <t>11/08/2026 14:14</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>11/08/2026 13:56</t>
+          <t>11/08/2026 14:21</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -5926,13 +5926,13 @@
         </is>
       </c>
       <c r="N40" s="2" t="n">
-        <v>46245.57777777778</v>
+        <v>46245.59305555555</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>46245.58055555556</v>
+        <v>46245.59791666667</v>
       </c>
       <c r="P40" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q40" s="3" t="n">
         <v>46245</v>
@@ -5964,7 +5964,9 @@
       <c r="Z40" t="b">
         <v>0</v>
       </c>
-      <c r="AA40" t="inlineStr"/>
+      <c r="AA40" t="n">
+        <v>480</v>
+      </c>
       <c r="AB40" t="b">
         <v>0</v>
       </c>
@@ -5973,10 +5975,10 @@
       </c>
       <c r="AD40" t="inlineStr"/>
       <c r="AE40" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF40" t="n">
-        <v>832</v>
+        <v>854</v>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
@@ -6001,7 +6003,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>16849341</v>
+        <v>16849345</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -6025,7 +6027,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>340 - 1 - R</t>
+          <t>410 - OU</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -6040,12 +6042,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>11/08/2026 13:56</t>
+          <t>11/08/2026 14:21</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>11/08/2026 14:01</t>
+          <t>11/08/2026 14:29</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -6062,13 +6064,13 @@
         </is>
       </c>
       <c r="N41" s="2" t="n">
-        <v>46245.58055555556</v>
+        <v>46245.59791666667</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>46245.58402777778</v>
+        <v>46245.60347222222</v>
       </c>
       <c r="P41" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q41" s="3" t="n">
         <v>46245</v>
@@ -6101,7 +6103,7 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>240</v>
+        <v>420</v>
       </c>
       <c r="AB41" t="b">
         <v>0</v>
@@ -6111,10 +6113,10 @@
       </c>
       <c r="AD41" t="inlineStr"/>
       <c r="AE41" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF41" t="n">
-        <v>836</v>
+        <v>861</v>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
@@ -6139,7 +6141,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>16849342</v>
+        <v>16849346</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -6163,7 +6165,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>340 - 2 - R</t>
+          <t>380 - OU</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6178,12 +6180,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>11/08/2026 14:02</t>
+          <t>11/08/2026 14:29</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>11/08/2026 14:05</t>
+          <t>11/08/2026 14:32</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -6200,10 +6202,10 @@
         </is>
       </c>
       <c r="N42" s="2" t="n">
-        <v>46245.58472222222</v>
+        <v>46245.60347222222</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>46245.58680555555</v>
+        <v>46245.60555555556</v>
       </c>
       <c r="P42" t="n">
         <v>3</v>
@@ -6239,7 +6241,7 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>360</v>
+        <v>480</v>
       </c>
       <c r="AB42" t="b">
         <v>0</v>
@@ -6252,7 +6254,7 @@
         <v>14</v>
       </c>
       <c r="AF42" t="n">
-        <v>842</v>
+        <v>869</v>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
@@ -6277,7 +6279,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>16849343</v>
+        <v>16849347</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -6291,7 +6293,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Q031</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -6301,7 +6303,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>370 - R</t>
+          <t>01 - TB</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6316,12 +6318,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>11/08/2026 14:06</t>
+          <t>11/08/2026 14:33</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>11/08/2026 14:10</t>
+          <t>11/08/2026 14:40</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -6338,13 +6340,13 @@
         </is>
       </c>
       <c r="N43" s="2" t="n">
-        <v>46245.5875</v>
+        <v>46245.60625</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>46245.59027777778</v>
+        <v>46245.61111111111</v>
       </c>
       <c r="P43" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>46245</v>
@@ -6390,7 +6392,7 @@
         <v>14</v>
       </c>
       <c r="AF43" t="n">
-        <v>846</v>
+        <v>873</v>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
@@ -6415,7 +6417,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>16849344</v>
+        <v>16849348</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -6429,17 +6431,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Q031</t>
+          <t>Q032</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Rua MONTEVIDEO</t>
+          <t>Rua ROBERTO BUENO DA SILVA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>400 - R</t>
+          <t>621 - 1 - R</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6454,12 +6456,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>11/08/2026 14:14</t>
+          <t>11/08/2026 14:41</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>11/08/2026 14:21</t>
+          <t>11/08/2026 14:47</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -6476,13 +6478,13 @@
         </is>
       </c>
       <c r="N44" s="2" t="n">
-        <v>46245.59305555555</v>
+        <v>46245.61180555556</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>46245.59791666667</v>
+        <v>46245.61597222222</v>
       </c>
       <c r="P44" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>46245</v>
@@ -6528,7 +6530,7 @@
         <v>14</v>
       </c>
       <c r="AF44" t="n">
-        <v>854</v>
+        <v>881</v>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
@@ -6553,7 +6555,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>16849345</v>
+        <v>16849349</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -6567,17 +6569,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Q031</t>
+          <t>Q032</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rua MONTEVIDEO</t>
+          <t>Rua ROBERTO BUENO DA SILVA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>410 - OU</t>
+          <t>621 - 2 - TB</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6592,12 +6594,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>11/08/2026 14:21</t>
+          <t>11/08/2026 14:47</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>11/08/2026 14:29</t>
+          <t>11/08/2026 14:58</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -6614,13 +6616,13 @@
         </is>
       </c>
       <c r="N45" s="2" t="n">
-        <v>46245.59791666667</v>
+        <v>46245.61597222222</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>46245.60347222222</v>
+        <v>46245.62361111111</v>
       </c>
       <c r="P45" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Q45" s="3" t="n">
         <v>46245</v>
@@ -6653,7 +6655,7 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>420</v>
+        <v>360</v>
       </c>
       <c r="AB45" t="b">
         <v>0</v>
@@ -6666,7 +6668,7 @@
         <v>14</v>
       </c>
       <c r="AF45" t="n">
-        <v>861</v>
+        <v>887</v>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
@@ -6691,7 +6693,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>16849346</v>
+        <v>16849350</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -6705,17 +6707,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Q031</t>
+          <t>Q032</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rua MONTEVIDEO</t>
+          <t>Rua ROBERTO BUENO DA SILVA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>380 - OU</t>
+          <t>609 - R</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6730,12 +6732,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>11/08/2026 14:29</t>
+          <t>11/08/2026 14:59</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>11/08/2026 14:32</t>
+          <t>11/08/2026 15:05</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -6752,13 +6754,13 @@
         </is>
       </c>
       <c r="N46" s="2" t="n">
-        <v>46245.60347222222</v>
+        <v>46245.62430555555</v>
       </c>
       <c r="O46" s="2" t="n">
-        <v>46245.60555555556</v>
+        <v>46245.62847222222</v>
       </c>
       <c r="P46" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>46245</v>
@@ -6791,7 +6793,7 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>480</v>
+        <v>720</v>
       </c>
       <c r="AB46" t="b">
         <v>0</v>
@@ -6804,7 +6806,7 @@
         <v>14</v>
       </c>
       <c r="AF46" t="n">
-        <v>869</v>
+        <v>899</v>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
@@ -6829,7 +6831,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>16849347</v>
+        <v>16849351</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -6843,17 +6845,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q032</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rua MONTEVIDEO</t>
+          <t>Rua ROBERTO BUENO DA SILVA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>01 - TB</t>
+          <t>597 - R</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6868,12 +6870,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>11/08/2026 14:33</t>
+          <t>11/08/2026 15:06</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>11/08/2026 14:40</t>
+          <t>11/08/2026 15:14</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -6890,13 +6892,13 @@
         </is>
       </c>
       <c r="N47" s="2" t="n">
-        <v>46245.60625</v>
+        <v>46245.62916666667</v>
       </c>
       <c r="O47" s="2" t="n">
-        <v>46245.61111111111</v>
+        <v>46245.63472222222</v>
       </c>
       <c r="P47" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q47" s="3" t="n">
         <v>46245</v>
@@ -6929,7 +6931,7 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>240</v>
+        <v>420</v>
       </c>
       <c r="AB47" t="b">
         <v>0</v>
@@ -6939,10 +6941,10 @@
       </c>
       <c r="AD47" t="inlineStr"/>
       <c r="AE47" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF47" t="n">
-        <v>873</v>
+        <v>906</v>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
@@ -6967,7 +6969,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>16849348</v>
+        <v>16849352</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -6991,7 +6993,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>621 - 1 - R</t>
+          <t>587 - R</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7006,12 +7008,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>11/08/2026 14:41</t>
+          <t>11/08/2026 15:16</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>11/08/2026 14:47</t>
+          <t>11/08/2026 15:24</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -7028,13 +7030,13 @@
         </is>
       </c>
       <c r="N48" s="2" t="n">
-        <v>46245.61180555556</v>
+        <v>46245.63611111111</v>
       </c>
       <c r="O48" s="2" t="n">
-        <v>46245.61597222222</v>
+        <v>46245.64166666667</v>
       </c>
       <c r="P48" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q48" s="3" t="n">
         <v>46245</v>
@@ -7067,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>480</v>
+        <v>600</v>
       </c>
       <c r="AB48" t="b">
         <v>0</v>
@@ -7077,10 +7079,10 @@
       </c>
       <c r="AD48" t="inlineStr"/>
       <c r="AE48" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF48" t="n">
-        <v>881</v>
+        <v>916</v>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
@@ -7105,7 +7107,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>16849349</v>
+        <v>16849353</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -7124,12 +7126,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rua ROBERTO BUENO DA SILVA</t>
+          <t>Avenida COSTA E SILVA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>621 - 2 - TB</t>
+          <t>573 - 1 - R</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7144,12 +7146,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>11/08/2026 14:47</t>
+          <t>11/08/2026 15:35</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>11/08/2026 14:58</t>
+          <t>11/08/2026 15:39</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -7166,13 +7168,13 @@
         </is>
       </c>
       <c r="N49" s="2" t="n">
-        <v>46245.61597222222</v>
+        <v>46245.64930555555</v>
       </c>
       <c r="O49" s="2" t="n">
-        <v>46245.62361111111</v>
+        <v>46245.65208333333</v>
       </c>
       <c r="P49" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Q49" s="3" t="n">
         <v>46245</v>
@@ -7205,7 +7207,7 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>360</v>
+        <v>1140</v>
       </c>
       <c r="AB49" t="b">
         <v>0</v>
@@ -7215,10 +7217,10 @@
       </c>
       <c r="AD49" t="inlineStr"/>
       <c r="AE49" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF49" t="n">
-        <v>887</v>
+        <v>935</v>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
@@ -7243,7 +7245,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>16849350</v>
+        <v>16849354</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -7262,12 +7264,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rua ROBERTO BUENO DA SILVA</t>
+          <t>Avenida COSTA E SILVA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>609 - R</t>
+          <t>570 - R</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7282,12 +7284,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>11/08/2026 14:59</t>
+          <t>11/08/2026 15:41</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>11/08/2026 15:05</t>
+          <t>11/08/2026 15:45</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -7304,13 +7306,13 @@
         </is>
       </c>
       <c r="N50" s="2" t="n">
-        <v>46245.62430555555</v>
+        <v>46245.65347222222</v>
       </c>
       <c r="O50" s="2" t="n">
-        <v>46245.62847222222</v>
+        <v>46245.65625</v>
       </c>
       <c r="P50" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q50" s="3" t="n">
         <v>46245</v>
@@ -7343,7 +7345,7 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>720</v>
+        <v>360</v>
       </c>
       <c r="AB50" t="b">
         <v>0</v>
@@ -7353,10 +7355,10 @@
       </c>
       <c r="AD50" t="inlineStr"/>
       <c r="AE50" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF50" t="n">
-        <v>899</v>
+        <v>941</v>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
@@ -7381,7 +7383,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>16849351</v>
+        <v>16849355</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -7400,12 +7402,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rua ROBERTO BUENO DA SILVA</t>
+          <t>Avenida COSTA E SILVA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>597 - R</t>
+          <t>582 - R</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7420,12 +7422,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>11/08/2026 15:06</t>
+          <t>11/08/2026 15:45</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>11/08/2026 15:14</t>
+          <t>11/08/2026 15:48</t>
         </is>
       </c>
       <c r="K51" t="n">
@@ -7442,13 +7444,13 @@
         </is>
       </c>
       <c r="N51" s="2" t="n">
-        <v>46245.62916666667</v>
+        <v>46245.65625</v>
       </c>
       <c r="O51" s="2" t="n">
-        <v>46245.63472222222</v>
+        <v>46245.65833333333</v>
       </c>
       <c r="P51" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q51" s="3" t="n">
         <v>46245</v>
@@ -7481,7 +7483,7 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>420</v>
+        <v>240</v>
       </c>
       <c r="AB51" t="b">
         <v>0</v>
@@ -7494,7 +7496,7 @@
         <v>15</v>
       </c>
       <c r="AF51" t="n">
-        <v>906</v>
+        <v>945</v>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
@@ -7519,7 +7521,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>16849352</v>
+        <v>16849356</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -7538,12 +7540,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rua ROBERTO BUENO DA SILVA</t>
+          <t>Avenida COSTA E SILVA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>587 - R</t>
+          <t>606 - C</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7558,12 +7560,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>11/08/2026 15:16</t>
+          <t>11/08/2026 15:48</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>11/08/2026 15:24</t>
+          <t>11/08/2026 15:51</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -7580,13 +7582,13 @@
         </is>
       </c>
       <c r="N52" s="2" t="n">
-        <v>46245.63611111111</v>
+        <v>46245.65833333333</v>
       </c>
       <c r="O52" s="2" t="n">
-        <v>46245.64166666667</v>
+        <v>46245.66041666667</v>
       </c>
       <c r="P52" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q52" s="3" t="n">
         <v>46245</v>
@@ -7619,7 +7621,7 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>600</v>
+        <v>180</v>
       </c>
       <c r="AB52" t="b">
         <v>0</v>
@@ -7632,7 +7634,7 @@
         <v>15</v>
       </c>
       <c r="AF52" t="n">
-        <v>916</v>
+        <v>948</v>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
@@ -7657,7 +7659,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>16849353</v>
+        <v>16849357</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -7676,12 +7678,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Avenida COSTA E SILVA</t>
+          <t>Rua ROBERTO BUENO DA SILVA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>573 - 1 - R</t>
+          <t>573 - R</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7696,12 +7698,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>11/08/2026 15:35</t>
+          <t>11/08/2026 15:56</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>11/08/2026 15:39</t>
+          <t>11/08/2026 16:00</t>
         </is>
       </c>
       <c r="K53" t="n">
@@ -7718,10 +7720,10 @@
         </is>
       </c>
       <c r="N53" s="2" t="n">
-        <v>46245.64930555555</v>
+        <v>46245.66388888889</v>
       </c>
       <c r="O53" s="2" t="n">
-        <v>46245.65208333333</v>
+        <v>46245.66666666666</v>
       </c>
       <c r="P53" t="n">
         <v>4</v>
@@ -7757,7 +7759,7 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1140</v>
+        <v>480</v>
       </c>
       <c r="AB53" t="b">
         <v>0</v>
@@ -7770,7 +7772,7 @@
         <v>15</v>
       </c>
       <c r="AF53" t="n">
-        <v>935</v>
+        <v>956</v>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
@@ -7795,7 +7797,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>16849354</v>
+        <v>16849358</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -7814,12 +7816,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Avenida COSTA E SILVA</t>
+          <t>Rua ROBERTO BUENO DA SILVA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>570 - R</t>
+          <t>621 - C</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7834,12 +7836,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>11/08/2026 15:41</t>
+          <t>11/08/2026 16:00</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>11/08/2026 15:45</t>
+          <t>11/08/2026 16:05</t>
         </is>
       </c>
       <c r="K54" t="n">
@@ -7856,13 +7858,13 @@
         </is>
       </c>
       <c r="N54" s="2" t="n">
-        <v>46245.65347222222</v>
+        <v>46245.66666666666</v>
       </c>
       <c r="O54" s="2" t="n">
-        <v>46245.65625</v>
+        <v>46245.67013888889</v>
       </c>
       <c r="P54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q54" s="3" t="n">
         <v>46245</v>
@@ -7895,7 +7897,7 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="AB54" t="b">
         <v>0</v>
@@ -7905,10 +7907,10 @@
       </c>
       <c r="AD54" t="inlineStr"/>
       <c r="AE54" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF54" t="n">
-        <v>941</v>
+        <v>960</v>
       </c>
       <c r="AG54" t="inlineStr">
         <is>
@@ -7933,7 +7935,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>16849355</v>
+        <v>16828940</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -7942,22 +7944,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>405 - ALTOS DA GLÓRIA</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Q032</t>
+          <t>Q012</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Avenida COSTA E SILVA</t>
+          <t>Rua DR. MIGUEL MARCONDES ARMANDO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>582 - R</t>
+          <t>926 - R</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7972,38 +7974,38 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>11/08/2026 15:45</t>
+          <t>10/08/2026 15:27</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>11/08/2026 15:48</t>
+          <t>10/08/2026 15:31</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>2721</v>
+        <v>3037</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="N55" s="2" t="n">
-        <v>46245.65625</v>
+        <v>46244.64375</v>
       </c>
       <c r="O55" s="2" t="n">
-        <v>46245.65833333333</v>
+        <v>46244.64652777778</v>
       </c>
       <c r="P55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q55" s="3" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="R55" t="n">
         <v>319</v>
@@ -8032,9 +8034,7 @@
       <c r="Z55" t="b">
         <v>0</v>
       </c>
-      <c r="AA55" t="n">
-        <v>240</v>
-      </c>
+      <c r="AA55" t="inlineStr"/>
       <c r="AB55" t="b">
         <v>0</v>
       </c>
@@ -8046,7 +8046,7 @@
         <v>15</v>
       </c>
       <c r="AF55" t="n">
-        <v>945</v>
+        <v>927</v>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>0</v>
       </c>
       <c r="AI55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ55" t="b">
         <v>0</v>
@@ -8071,7 +8071,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>16849356</v>
+        <v>16828941</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -8080,22 +8080,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>405 - ALTOS DA GLÓRIA</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Q032</t>
+          <t>Q012</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Avenida COSTA E SILVA</t>
+          <t>Rua RENE ZAMLUTTI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>606 - C</t>
+          <t>355 - R</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -8110,38 +8110,38 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>11/08/2026 15:48</t>
+          <t>10/08/2026 15:32</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>11/08/2026 15:51</t>
+          <t>10/08/2026 15:35</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>2721</v>
+        <v>3037</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="N56" s="2" t="n">
-        <v>46245.65833333333</v>
+        <v>46244.64722222222</v>
       </c>
       <c r="O56" s="2" t="n">
-        <v>46245.66041666667</v>
+        <v>46244.64930555555</v>
       </c>
       <c r="P56" t="n">
         <v>3</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="R56" t="n">
         <v>319</v>
@@ -8171,7 +8171,7 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="AB56" t="b">
         <v>0</v>
@@ -8184,7 +8184,7 @@
         <v>15</v>
       </c>
       <c r="AF56" t="n">
-        <v>948</v>
+        <v>932</v>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         <v>0</v>
       </c>
       <c r="AI56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ56" t="b">
         <v>0</v>
@@ -8209,7 +8209,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>16849357</v>
+        <v>16828942</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -8218,22 +8218,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>405 - ALTOS DA GLÓRIA</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Q032</t>
+          <t>Q012</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rua ROBERTO BUENO DA SILVA</t>
+          <t>Rua RENE ZAMLUTTI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>573 - R</t>
+          <t>377 - R</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8248,38 +8248,38 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>11/08/2026 15:56</t>
+          <t>10/08/2026 15:35</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>11/08/2026 16:00</t>
+          <t>10/08/2026 15:38</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>2721</v>
+        <v>3037</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="N57" s="2" t="n">
-        <v>46245.66388888889</v>
+        <v>46244.64930555555</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>46245.66666666666</v>
+        <v>46244.65138888889</v>
       </c>
       <c r="P57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q57" s="3" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="R57" t="n">
         <v>319</v>
@@ -8309,7 +8309,7 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>480</v>
+        <v>180</v>
       </c>
       <c r="AB57" t="b">
         <v>0</v>
@@ -8322,7 +8322,7 @@
         <v>15</v>
       </c>
       <c r="AF57" t="n">
-        <v>956</v>
+        <v>935</v>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>0</v>
       </c>
       <c r="AI57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ57" t="b">
         <v>0</v>
@@ -8347,7 +8347,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>16849358</v>
+        <v>16828943</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -8356,22 +8356,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>405 - ALTOS DA GLÓRIA</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Q032</t>
+          <t>Q001</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rua ROBERTO BUENO DA SILVA</t>
+          <t>Rua ELOAH VIEIRA DA SILVA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>621 - C</t>
+          <t>928 - R</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8381,43 +8381,43 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Recuperação</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>11/08/2026 16:00</t>
+          <t>10/08/2026 15:41</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>11/08/2026 16:05</t>
+          <t>10/08/2026 15:47</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>2721</v>
+        <v>3037</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="N58" s="2" t="n">
-        <v>46245.66666666666</v>
+        <v>46244.65347222222</v>
       </c>
       <c r="O58" s="2" t="n">
-        <v>46245.67013888889</v>
+        <v>46244.65763888889</v>
       </c>
       <c r="P58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q58" s="3" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="R58" t="n">
         <v>319</v>
@@ -8447,7 +8447,7 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
       <c r="AB58" t="b">
         <v>0</v>
@@ -8457,10 +8457,10 @@
       </c>
       <c r="AD58" t="inlineStr"/>
       <c r="AE58" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF58" t="n">
-        <v>960</v>
+        <v>941</v>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         <v>0</v>
       </c>
       <c r="AI58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ58" t="b">
         <v>0</v>
